--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://v7hfx-my.sharepoint.com/personal/joseca20_v7hfx_onmicrosoft_com/Documents/web scraping/statsFutbol/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EDA0BE9-CF94-48EF-82DF-76D7B9226599}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7F57AA5-B9DA-432F-9A57-20D620A8F3FB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -510,9 +510,6 @@
     <t>n-s-america/argentina/club-de-gimnasia-la-plata</t>
   </si>
   <si>
-    <t>n-s-america/argentina/godoy-cruz</t>
-  </si>
-  <si>
     <t>n-s-america/argentina/club-atletico-huracan</t>
   </si>
   <si>
@@ -546,9 +543,6 @@
     <t>n-s-america/argentina/san-lorenzo-de-almagro</t>
   </si>
   <si>
-    <t>n-s-america/argentina/san-martin-de-san-juan</t>
-  </si>
-  <si>
     <t>n-s-america/argentina/club-atletico-sarmiento-junin</t>
   </si>
   <si>
@@ -1903,6 +1897,12 @@
   </si>
   <si>
     <t>n-s-america/ecuador/leones-fc</t>
+  </si>
+  <si>
+    <t>n-s-america/argentina/estudiantes-de-rio-cuarto</t>
+  </si>
+  <si>
+    <t>n-s-america/argentina/club-gimnasia-de-mendoza</t>
   </si>
 </sst>
 </file>
@@ -2407,7 +2407,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2438,7 +2438,7 @@
         <v>46044</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2468,7 +2468,7 @@
         <v>46030</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2498,7 +2498,7 @@
         <v>46059</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2528,7 +2528,7 @@
         <v>46038</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2558,7 +2558,7 @@
         <v>46050</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2588,7 +2588,7 @@
         <v>46060</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2618,7 +2618,7 @@
         <v>46052</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2648,7 +2648,7 @@
         <v>46039</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2678,7 +2678,7 @@
         <v>46045</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2708,7 +2708,7 @@
         <v>46053</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2738,16 +2738,16 @@
         <v>46059</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-de-gimnasia-la-plata</v>
+        <v>estudiantes-de-rio-cuarto</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>613</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2762,22 +2762,22 @@
       </c>
       <c r="H13" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="I13" s="10">
         <v>46073</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>godoy-cruz</v>
+        <v>club-de-gimnasia-la-plata</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2798,16 +2798,16 @@
         <v>46030</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-huracan</v>
+        <v>club-gimnasia-de-mendoza</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>614</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2832,10 +2832,10 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-sportivo-independiente-rivadavia</v>
+        <v>club-atletico-huracan</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C16" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2856,16 +2856,16 @@
         <v>46030</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-independiente</v>
+        <v>club-sportivo-independiente-rivadavia</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C17" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2886,16 +2886,16 @@
         <v>46030</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>instituto-atletico-central-cordoba</v>
+        <v>club-atletico-independiente</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C18" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2916,16 +2916,16 @@
         <v>46030</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-lanus</v>
+        <v>instituto-atletico-central-cordoba</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C19" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2946,16 +2946,16 @@
         <v>46030</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-newells-old-boys</v>
+        <v>club-atletico-lanus</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2976,16 +2976,16 @@
         <v>46031</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-platense</v>
+        <v>club-atletico-newells-old-boys</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C21" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3006,16 +3006,16 @@
         <v>46030</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>racing-club-de-avellaneda</v>
+        <v>club-atletico-platense</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C22" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3040,10 +3040,10 @@
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-river-plate</v>
+        <v>racing-club-de-avellaneda</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C23" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3064,16 +3064,16 @@
         <v>46052</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-rosario-central</v>
+        <v>club-atletico-river-plate</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C24" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3094,16 +3094,16 @@
         <v>46052</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>san-lorenzo-de-almagro</v>
+        <v>club-atletico-rosario-central</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C25" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3124,16 +3124,16 @@
         <v>46030</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>san-martin-de-san-juan</v>
+        <v>san-lorenzo-de-almagro</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C26" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3154,7 +3154,7 @@
         <v>46038</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -3163,7 +3163,7 @@
         <v>club-atletico-sarmiento-junin</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C27" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3184,7 +3184,7 @@
         <v>46030</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -3193,7 +3193,7 @@
         <v>club-atletico-talleres</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C28" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3214,7 +3214,7 @@
         <v>46030</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -3223,7 +3223,7 @@
         <v>club-atletico-tigre</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C29" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3244,7 +3244,7 @@
         <v>46030</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -3253,7 +3253,7 @@
         <v>club-atletico-union-de-santa-fe</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C30" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3281,7 +3281,7 @@
         <v>club-atletico-velez-sarsfield</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C31" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3302,7 +3302,7 @@
         <v>46036</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -3311,7 +3311,7 @@
         <v>adelaide-united-fc</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3332,7 +3332,7 @@
         <v>46039</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -3341,7 +3341,7 @@
         <v>auckland-fc</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3356,13 +3356,13 @@
       </c>
       <c r="H33" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="I33" s="10">
         <v>46074</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -3371,7 +3371,7 @@
         <v>brisbane-roar-fc</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C34" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3388,7 +3388,7 @@
         <v>central-coast-mariners-fc</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3405,7 +3405,7 @@
         <v>macarthur-fc</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3422,7 +3422,7 @@
         <v>melbourne-city-fc</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3439,7 +3439,7 @@
         <v>melbourne-victory-fc</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3456,7 +3456,7 @@
         <v>newcastle-jets-fc</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3473,7 +3473,7 @@
         <v>perth-glory-fc</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C40" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3490,7 +3490,7 @@
         <v>sydney-fc</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3507,7 +3507,7 @@
         <v>wellington-phoenix-fc</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3524,7 +3524,7 @@
         <v>western-sydney-wanderers-fc</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4017,7 +4017,7 @@
         <v>club-athletico-paranaense</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C72" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4102,7 +4102,7 @@
         <v>associacao-chapecoense-de-futebol</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C77" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4136,7 +4136,7 @@
         <v>coritiba-football-club</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C79" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4272,7 +4272,7 @@
         <v>clube-do-remo</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C87" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4629,7 +4629,7 @@
         <v>audax-italiano</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C108" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4646,7 +4646,7 @@
         <v>cd-cobresal</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C109" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4663,7 +4663,7 @@
         <v>colo-colo</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C110" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4680,7 +4680,7 @@
         <v>coquimbo-unido</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C111" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4697,7 +4697,7 @@
         <v>deportes-concepcion</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C112" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4714,7 +4714,7 @@
         <v>everton-de-vina-del-mar</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C113" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4731,7 +4731,7 @@
         <v>cd-huachipato</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C114" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4748,7 +4748,7 @@
         <v>deportes-la-serena</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C115" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4765,7 +4765,7 @@
         <v>deportes-limache</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C116" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4782,7 +4782,7 @@
         <v>deportivo-nublense</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C117" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4799,7 +4799,7 @@
         <v>o-higgins-fc</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C118" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4816,7 +4816,7 @@
         <v>cd-palestino</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C119" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4833,7 +4833,7 @@
         <v>union-la-calera</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C120" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4850,7 +4850,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C121" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4867,7 +4867,7 @@
         <v>club-universidad-de-chile</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C122" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4884,7 +4884,7 @@
         <v>cd-universidad-de-concepcion</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C123" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5003,7 +5003,7 @@
         <v>cucuta-deportivo-fc</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C130" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5071,7 +5071,7 @@
         <v>internacional-de-bogota</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C134" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5088,7 +5088,7 @@
         <v>jaguares-de-cordoba</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C135" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5241,7 +5241,7 @@
         <v>dinamo-zagreb</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C144" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5258,7 +5258,7 @@
         <v>gorica</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C145" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5275,7 +5275,7 @@
         <v>hajduk-split</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C146" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5292,7 +5292,7 @@
         <v>istra-1961</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C147" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5309,7 +5309,7 @@
         <v>lokomotiva-zagreb</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C148" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5326,7 +5326,7 @@
         <v>osijek</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C149" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5343,7 +5343,7 @@
         <v>rijeka</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C150" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5360,7 +5360,7 @@
         <v>slaven-belupo</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C151" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5377,7 +5377,7 @@
         <v>varazdin</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C152" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5394,7 +5394,7 @@
         <v>hnk-vukovar-1991</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C153" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5411,7 +5411,7 @@
         <v>bohemians-1905</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C154" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5428,7 +5428,7 @@
         <v>fk-dukla-prague</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C155" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5445,7 +5445,7 @@
         <v>fc-hradec-kralove</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C156" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5462,7 +5462,7 @@
         <v>fk-jablonec</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C157" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5479,7 +5479,7 @@
         <v>mfk-karvina</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C158" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5496,7 +5496,7 @@
         <v>fc-slovan-liberec</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C159" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5513,7 +5513,7 @@
         <v>fk-mlada-boleslav</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C160" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5530,7 +5530,7 @@
         <v>fc-banik-ostrava</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C161" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5547,7 +5547,7 @@
         <v>fk-pardubice</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C162" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5564,7 +5564,7 @@
         <v>fc-viktoria-plzen</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C163" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5581,7 +5581,7 @@
         <v>sk-sigma-olomouc</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C164" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5598,7 +5598,7 @@
         <v>slavia-prague</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C165" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5615,7 +5615,7 @@
         <v>fc-slovacko</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C166" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5632,7 +5632,7 @@
         <v>sparta-prague</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C167" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5649,7 +5649,7 @@
         <v>fk-teplice</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C168" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5666,7 +5666,7 @@
         <v>fc-fastav-zlin</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C169" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5683,7 +5683,7 @@
         <v>aarhus</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C170" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5700,7 +5700,7 @@
         <v>brondby</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C171" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5717,7 +5717,7 @@
         <v>fc-copenhagen</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C172" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5734,7 +5734,7 @@
         <v>fc-fredericia</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C173" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5751,7 +5751,7 @@
         <v>fc-midtjylland</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C174" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5768,7 +5768,7 @@
         <v>fc-nordsjaelland</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C175" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5785,7 +5785,7 @@
         <v>odense-boldklub</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C176" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5802,7 +5802,7 @@
         <v>randers-fc</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C177" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5819,7 +5819,7 @@
         <v>silkeborg-if</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C178" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5836,7 +5836,7 @@
         <v>sonderjyske</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C179" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5853,7 +5853,7 @@
         <v>vejle-bk</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C180" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5870,7 +5870,7 @@
         <v>viborg-ff</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C181" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5887,7 +5887,7 @@
         <v>sd-aucas</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C182" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D182" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -5904,7 +5904,7 @@
         <v>barcelona-sc</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C183" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D183" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -5921,7 +5921,7 @@
         <v>delfin-sc</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C184" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D184" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -5938,7 +5938,7 @@
         <v>cd-cuenca</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D185" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -5955,7 +5955,7 @@
         <v>cs-emelec</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="D186" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -5972,7 +5972,7 @@
         <v>guayaquil-city-fc</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C187" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="D187" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -5989,7 +5989,7 @@
         <v>csd-independiente-del-valle</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C188" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="D188" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -6006,7 +6006,7 @@
         <v>ldu-quito</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C189" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="D189" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -6023,7 +6023,7 @@
         <v>leones-fc</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C190" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D190" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -6040,7 +6040,7 @@
         <v>libertad-fc</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C191" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D191" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -6057,7 +6057,7 @@
         <v>csd-macara</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C192" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="D192" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -6074,7 +6074,7 @@
         <v>manta-fc</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C193" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D193" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -6091,7 +6091,7 @@
         <v>mushuc-runa-sc</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C194" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="D194" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -6108,7 +6108,7 @@
         <v>orense-sc</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C195" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="D195" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -6125,7 +6125,7 @@
         <v>tecnico-universitario</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C196" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="D196" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C197" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="D197" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -6499,7 +6499,7 @@
         <v>birmingham-city-fc</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C218" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6516,7 +6516,7 @@
         <v>blackburn-rovers-fc</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C219" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6533,7 +6533,7 @@
         <v>bristol-city-fc</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C220" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6550,7 +6550,7 @@
         <v>charlton-athletic-fc</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C221" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6567,7 +6567,7 @@
         <v>coventry-city-fc</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C222" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6584,7 +6584,7 @@
         <v>derby-county-fc</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C223" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6601,7 +6601,7 @@
         <v>hull-city-fc</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C224" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6618,7 +6618,7 @@
         <v>ipswich-town-fc</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C225" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6635,7 +6635,7 @@
         <v>leicester-city-fc</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C226" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6652,7 +6652,7 @@
         <v>middlesbrough-fc</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C227" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6669,7 +6669,7 @@
         <v>millwall-fc</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C228" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6686,7 +6686,7 @@
         <v>norwich-city-fc</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C229" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6703,7 +6703,7 @@
         <v>oxford-united-fc</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C230" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6720,7 +6720,7 @@
         <v>portsmouth-fc</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C231" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6737,7 +6737,7 @@
         <v>preston-north-end-fc</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C232" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6754,7 +6754,7 @@
         <v>queens-park-rangers-fc</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C233" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6771,7 +6771,7 @@
         <v>sheffield-united-fc</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C234" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6788,7 +6788,7 @@
         <v>sheffield-wednesday-fc</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C235" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6805,7 +6805,7 @@
         <v>southampton-fc</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C236" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6822,7 +6822,7 @@
         <v>stoke-city-fc</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C237" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6839,7 +6839,7 @@
         <v>swansea-city-afc</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C238" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6856,7 +6856,7 @@
         <v>watford-fc</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C239" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6873,7 +6873,7 @@
         <v>west-bromwich-albion-fc</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C240" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6890,7 +6890,7 @@
         <v>wrexham-afc</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C241" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6907,7 +6907,7 @@
         <v>if-gnistan</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6924,7 +6924,7 @@
         <v>fc-haka</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6941,7 +6941,7 @@
         <v>hjk-helsinki</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6958,7 +6958,7 @@
         <v>fc-ilves</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C245" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6975,7 +6975,7 @@
         <v>fc-inter-turku</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C246" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6992,7 +6992,7 @@
         <v>ff-jaro</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C247" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7009,7 +7009,7 @@
         <v>kotkan-tyovaen-palloilijat</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C248" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7026,7 +7026,7 @@
         <v>kuopion-palloseura</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7043,7 +7043,7 @@
         <v>ifk-mariehamn</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7060,7 +7060,7 @@
         <v>ac-oulu</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7077,7 +7077,7 @@
         <v>sjk</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C252" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7094,7 +7094,7 @@
         <v>vaasan-palloseura</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C253" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7111,7 +7111,7 @@
         <v>angers-sco</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C254" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7128,7 +7128,7 @@
         <v>aj-auxerre</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C255" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7145,7 +7145,7 @@
         <v>stade-brestois-29</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C256" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7162,7 +7162,7 @@
         <v>le-havre-ac</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C257" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7179,7 +7179,7 @@
         <v>rc-lens</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C258" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7196,7 +7196,7 @@
         <v>lille-osc</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C259" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7213,7 +7213,7 @@
         <v>fc-lorient</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C260" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7230,7 +7230,7 @@
         <v>olympique-lyonnais</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C261" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7247,7 +7247,7 @@
         <v>olympique-de-marseille</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C262" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7264,7 +7264,7 @@
         <v>fc-metz</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C263" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7281,7 +7281,7 @@
         <v>as-monaco-fc</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C264" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7298,7 +7298,7 @@
         <v>fc-nantes</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C265" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7315,7 +7315,7 @@
         <v>ogc-nice</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C266" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7332,7 +7332,7 @@
         <v>paris-fc</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C267" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7349,7 +7349,7 @@
         <v>paris-saint-germain-fc</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C268" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7366,7 +7366,7 @@
         <v>stade-rennais-fc</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C269" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7383,7 +7383,7 @@
         <v>rc-strasbourg-alsace</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C270" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7400,7 +7400,7 @@
         <v>toulouse-fc</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C271" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7791,7 +7791,7 @@
         <v>fc-koln</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C294" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7842,7 +7842,7 @@
         <v>hamburger-sv</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C297" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8029,7 +8029,7 @@
         <v>arminia-bielefeld</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C308" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8063,7 +8063,7 @@
         <v>eintracht-braunschweig</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C310" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8080,7 +8080,7 @@
         <v>darmstadt-98</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C311" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8097,7 +8097,7 @@
         <v>dynamo-dresden</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C312" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8114,7 +8114,7 @@
         <v>fortuna-dusseldorf</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C313" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8131,7 +8131,7 @@
         <v>sv-elversberg</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C314" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8148,7 +8148,7 @@
         <v>greuther-furth</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C315" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8165,7 +8165,7 @@
         <v>hannover-96</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C316" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8182,7 +8182,7 @@
         <v>hertha-berlin</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C317" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8199,7 +8199,7 @@
         <v>fc-kaiserslautern</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C318" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8216,7 +8216,7 @@
         <v>karlsruher-sc</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C319" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8250,7 +8250,7 @@
         <v>fc-magdeburg</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C321" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8267,7 +8267,7 @@
         <v>preussen-munster</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C322" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8284,7 +8284,7 @@
         <v>fc-nurnberg</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C323" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8301,7 +8301,7 @@
         <v>sc-paderborn</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C324" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8318,7 +8318,7 @@
         <v>schalke-04</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C325" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8335,7 +8335,7 @@
         <v>aek-athens-fc</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C326" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8352,7 +8352,7 @@
         <v>ael-fc</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C327" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8369,7 +8369,7 @@
         <v>aris-thessaloniki-fc</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C328" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8386,7 +8386,7 @@
         <v>asteras-tripolis-fc</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8403,7 +8403,7 @@
         <v>atromitos-fc</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C330" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8420,7 +8420,7 @@
         <v>ae-kifisia-fc</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C331" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8437,7 +8437,7 @@
         <v>levadiakos-fc</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C332" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8454,7 +8454,7 @@
         <v>ofi-crete-fc</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C333" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8471,7 +8471,7 @@
         <v>olympiacos-fc</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C334" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8488,7 +8488,7 @@
         <v>panathinaikos-fc</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C335" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8505,7 +8505,7 @@
         <v>panetolikos-fc</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C336" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8522,7 +8522,7 @@
         <v>panserraikos-fc</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C337" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8539,7 +8539,7 @@
         <v>paok-fc</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C338" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8556,7 +8556,7 @@
         <v>volos-fc</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C339" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8573,7 +8573,7 @@
         <v>ac-milan</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C340" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8590,7 +8590,7 @@
         <v>as-roma</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C341" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8607,7 +8607,7 @@
         <v>atalanta-bc</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C342" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8624,7 +8624,7 @@
         <v>bologna-fc-1909</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C343" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8641,7 +8641,7 @@
         <v>cagliari-calcio</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C344" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8658,7 +8658,7 @@
         <v>como-1907</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C345" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8675,7 +8675,7 @@
         <v>us-cremonese</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C346" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8692,7 +8692,7 @@
         <v>acf-fiorentina</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C347" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8709,7 +8709,7 @@
         <v>genoa-cfc</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C348" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8726,7 +8726,7 @@
         <v>inter-milan</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C349" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8743,7 +8743,7 @@
         <v>juventus-fc</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C350" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8760,7 +8760,7 @@
         <v>ss-lazio</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C351" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8777,7 +8777,7 @@
         <v>us-lecce</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C352" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8794,7 +8794,7 @@
         <v>ssc-napoli</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C353" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8811,7 +8811,7 @@
         <v>parma-calcio-1913</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C354" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8828,7 +8828,7 @@
         <v>ac-pisa-1909</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C355" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8845,7 +8845,7 @@
         <v>us-sassuolo-calcio</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C356" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8862,7 +8862,7 @@
         <v>torino-fc</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C357" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8879,7 +8879,7 @@
         <v>udinese-calcio</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C358" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8896,7 +8896,7 @@
         <v>hellas-verona-fc</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C359" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8913,7 +8913,7 @@
         <v>atletico-san-luis</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C360" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8930,7 +8930,7 @@
         <v>atlas-fc</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C361" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8947,7 +8947,7 @@
         <v>club-america</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C362" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8964,7 +8964,7 @@
         <v>cruz-azul</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C363" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8981,7 +8981,7 @@
         <v>cd-guadalajara</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C364" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8998,7 +8998,7 @@
         <v>fc-juarez</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C365" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9015,7 +9015,7 @@
         <v>club-leon</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C366" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9032,7 +9032,7 @@
         <v>mazatlan-fc</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C367" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9049,7 +9049,7 @@
         <v>cf-monterrey</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C368" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9066,7 +9066,7 @@
         <v>club-necaxa</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C369" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9083,7 +9083,7 @@
         <v>cf-pachuca</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C370" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9100,7 +9100,7 @@
         <v>club-puebla</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C371" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9117,7 +9117,7 @@
         <v>queretaro-fc</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C372" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9134,7 +9134,7 @@
         <v>santos-laguna</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C373" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9151,7 +9151,7 @@
         <v>tigres-uanl</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C374" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9168,7 +9168,7 @@
         <v>club-tijuana</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C375" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9185,7 +9185,7 @@
         <v>deportivo-toluca-fc</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C376" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9202,7 +9202,7 @@
         <v>unam</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C377" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9219,7 +9219,7 @@
         <v>afc-ajax</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C378" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9236,7 +9236,7 @@
         <v>az-alkmaar</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C379" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9253,7 +9253,7 @@
         <v>sbv-excelsior</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C380" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9270,7 +9270,7 @@
         <v>fc-volendam</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C381" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9287,7 +9287,7 @@
         <v>feyenoord-rotterdam</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C382" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9304,7 +9304,7 @@
         <v>go-ahead-eagles</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C383" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9321,7 +9321,7 @@
         <v>fc-groningen</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C384" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9338,7 +9338,7 @@
         <v>sc-heerenveen</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C385" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9355,7 +9355,7 @@
         <v>heracles-almelo</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C386" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9372,7 +9372,7 @@
         <v>nac-breda</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C387" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9389,7 +9389,7 @@
         <v>nec-nijmegen</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C388" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9406,7 +9406,7 @@
         <v>psv-eindhoven</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C389" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9423,7 +9423,7 @@
         <v>fortuna-sittard</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C390" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9440,7 +9440,7 @@
         <v>sparta-rotterdam</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C391" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9457,7 +9457,7 @@
         <v>sc-telstar</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C392" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9474,7 +9474,7 @@
         <v>fc-twente</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C393" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9491,7 +9491,7 @@
         <v>fc-utrecht</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C394" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9508,7 +9508,7 @@
         <v>pec-zwolle</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C395" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9525,7 +9525,7 @@
         <v>fk-bodo-glimt</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C396" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9542,7 +9542,7 @@
         <v>sk-brann</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C397" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9559,7 +9559,7 @@
         <v>bryne-fk</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C398" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9576,7 +9576,7 @@
         <v>fredrikstad-fk</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C399" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9593,7 +9593,7 @@
         <v>ham-kam</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C400" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9610,7 +9610,7 @@
         <v>fk-haugesund</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C401" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9627,7 +9627,7 @@
         <v>kfum-kameratene-oslo</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C402" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9644,7 +9644,7 @@
         <v>kristiansund-bk</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C403" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9661,7 +9661,7 @@
         <v>molde-fk</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C404" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9678,7 +9678,7 @@
         <v>rosenborg-bk</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C405" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9695,7 +9695,7 @@
         <v>sandefjord-fotball</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C406" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9712,7 +9712,7 @@
         <v>sarpsborg-08-ff</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C407" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9729,7 +9729,7 @@
         <v>stromsgodset</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C408" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9746,7 +9746,7 @@
         <v>tromso-il</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C409" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9763,7 +9763,7 @@
         <v>valerenga-fotball</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C410" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9780,7 +9780,7 @@
         <v>viking-fk</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C411" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9797,7 +9797,7 @@
         <v>alianza-lima</v>
       </c>
       <c r="B412" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C412" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9814,7 +9814,7 @@
         <v>asociacion-deportiva-tarma</v>
       </c>
       <c r="B413" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C413" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9831,7 +9831,7 @@
         <v>alianza-atletico</v>
       </c>
       <c r="B414" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C414" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9848,7 +9848,7 @@
         <v>universidad-tecnica-de-cajamarca</v>
       </c>
       <c r="B415" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C415" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9865,7 +9865,7 @@
         <v>club-sportivo-cienciano</v>
       </c>
       <c r="B416" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C416" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9882,7 +9882,7 @@
         <v>comerciantes-unidos</v>
       </c>
       <c r="B417" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C417" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9899,7 +9899,7 @@
         <v>cusco-fc</v>
       </c>
       <c r="B418" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C418" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9916,7 +9916,7 @@
         <v>deportivo-garcilaso</v>
       </c>
       <c r="B419" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C419" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9933,7 +9933,7 @@
         <v>fc-cajamarca</v>
       </c>
       <c r="B420" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C420" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9950,7 +9950,7 @@
         <v>atletico-grau</v>
       </c>
       <c r="B421" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C421" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9967,7 +9967,7 @@
         <v>sport-huancayo</v>
       </c>
       <c r="B422" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C422" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9984,7 +9984,7 @@
         <v>adc-juan-pablo-ii-college</v>
       </c>
       <c r="B423" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C423" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10001,7 +10001,7 @@
         <v>los-chankas-cyc</v>
       </c>
       <c r="B424" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C424" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10018,7 +10018,7 @@
         <v>fbc-melgar</v>
       </c>
       <c r="B425" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C425" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10035,7 +10035,7 @@
         <v>club-deportivo-moquegua</v>
       </c>
       <c r="B426" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C426" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10052,7 +10052,7 @@
         <v>sport-boys</v>
       </c>
       <c r="B427" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C427" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10069,7 +10069,7 @@
         <v>sporting-cristal</v>
       </c>
       <c r="B428" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C428" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10086,7 +10086,7 @@
         <v>club-universitario-de-deportes</v>
       </c>
       <c r="B429" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C429" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10103,7 +10103,7 @@
         <v>arka-gdynia</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C430" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10120,7 +10120,7 @@
         <v>cracovia</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C431" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10137,7 +10137,7 @@
         <v>gornik-zabrze</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C432" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10154,7 +10154,7 @@
         <v>jagiellona-bialystok</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C433" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10171,7 +10171,7 @@
         <v>gks-katowice</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C434" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10188,7 +10188,7 @@
         <v>korona-kielce</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C435" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10205,7 +10205,7 @@
         <v>lech-poznan</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C436" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10222,7 +10222,7 @@
         <v>lechia-gdansk</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C437" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10239,7 +10239,7 @@
         <v>legia-warsaw</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C438" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10256,7 +10256,7 @@
         <v>motor-lublin</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C439" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10273,7 +10273,7 @@
         <v>piast-gliwice</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C440" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10290,7 +10290,7 @@
         <v>mks-pogon-szczecin</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C441" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10307,7 +10307,7 @@
         <v>radomiak-radom</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C442" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10324,7 +10324,7 @@
         <v>rakow-czestochowa</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C443" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10341,7 +10341,7 @@
         <v>bruk-bet-termalica-nieciecza</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C444" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10358,7 +10358,7 @@
         <v>rts-widzew-lodz</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C445" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10375,7 +10375,7 @@
         <v>wisla-plock</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C446" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10392,7 +10392,7 @@
         <v>zaglebie-lubin</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C447" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10409,7 +10409,7 @@
         <v>avs-futebol-sad</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C448" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10426,7 +10426,7 @@
         <v>fc-alverca</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C449" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10443,7 +10443,7 @@
         <v>fc-arouca</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C450" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10460,7 +10460,7 @@
         <v>benfica</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C451" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10477,7 +10477,7 @@
         <v>braga</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C452" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10494,7 +10494,7 @@
         <v>casa-pia-ac</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C453" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10511,7 +10511,7 @@
         <v>gd-estoril-praia</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C454" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10528,7 +10528,7 @@
         <v>cf-estrela-da-amadora</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C455" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10545,7 +10545,7 @@
         <v>famalicao</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C456" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10562,7 +10562,7 @@
         <v>fc-porto</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C457" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10579,7 +10579,7 @@
         <v>gil-vicente</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C458" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10596,7 +10596,7 @@
         <v>vitoria-de-guimaraes</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C459" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10613,7 +10613,7 @@
         <v>moreirense-fc</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C460" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10630,7 +10630,7 @@
         <v>cd-nacional</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C461" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10647,7 +10647,7 @@
         <v>rio-ave-fc</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C462" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10664,7 +10664,7 @@
         <v>santa-clara</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C463" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10681,7 +10681,7 @@
         <v>sporting-cp</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C464" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10698,7 +10698,7 @@
         <v>cd-tondela</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C465" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10715,7 +10715,7 @@
         <v>fc-botosani</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C466" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10732,7 +10732,7 @@
         <v>cfr-cluj</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C467" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10749,7 +10749,7 @@
         <v>fk-miercurea-ciuc</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C468" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10766,7 +10766,7 @@
         <v>fc-dinamo-bucuresti</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C469" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10783,7 +10783,7 @@
         <v>fc-farul-constanta</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C470" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10800,7 +10800,7 @@
         <v>fc-arges-pitesti</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C471" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10817,7 +10817,7 @@
         <v>fc-hermannstadt</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C472" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10834,7 +10834,7 @@
         <v>fc-rapid-bucuresti</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C473" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10851,7 +10851,7 @@
         <v>fcsb</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C474" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10868,7 +10868,7 @@
         <v>fc-metaloglobus-bucuresti</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C475" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10885,7 +10885,7 @@
         <v>asc-otelul-galati</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C476" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10902,7 +10902,7 @@
         <v>fc-petrolul-ploiesti</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C477" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10919,7 +10919,7 @@
         <v>fc-universitatea-cluj</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C478" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10936,7 +10936,7 @@
         <v>afc-unirea-slobozia</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C479" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10953,7 +10953,7 @@
         <v>cs-universitatea-craiova</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C480" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10970,7 +10970,7 @@
         <v>fc-uta-arad</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C481" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10987,7 +10987,7 @@
         <v>al-fateh-sc</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C482" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11004,7 +11004,7 @@
         <v>al-fayha-fc</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C483" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11021,7 +11021,7 @@
         <v>al-hazem-fc</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C484" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11038,7 +11038,7 @@
         <v>khaleej-fc</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C485" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11055,7 +11055,7 @@
         <v>al-kholood-club</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C486" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11072,7 +11072,7 @@
         <v>al-najma-sc</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C487" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11089,7 +11089,7 @@
         <v>al-okhdood-club</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C488" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11106,7 +11106,7 @@
         <v>al-qadsiah-fc</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C489" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11123,7 +11123,7 @@
         <v>al-riyadh-sc</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C490" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11140,7 +11140,7 @@
         <v>al-ahli-saudi-fc</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C491" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11157,7 +11157,7 @@
         <v>al-ettifaq-fc</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C492" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11174,7 +11174,7 @@
         <v>al-hilal-fc</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C493" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11191,7 +11191,7 @@
         <v>al-ittihad-fc</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C494" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11208,7 +11208,7 @@
         <v>al-nassr-fc</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C495" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11225,7 +11225,7 @@
         <v>al-shabab-fc</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C496" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11242,7 +11242,7 @@
         <v>al-taawoun-fc</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C497" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11259,7 +11259,7 @@
         <v>damac-fc</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C498" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11276,7 +11276,7 @@
         <v>neom-sc</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C499" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11293,7 +11293,7 @@
         <v>aberdeen-fc</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C500" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11310,7 +11310,7 @@
         <v>celtic-fc</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C501" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11327,7 +11327,7 @@
         <v>dundee-fc</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C502" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11344,7 +11344,7 @@
         <v>dundee-united-fc</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C503" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11361,7 +11361,7 @@
         <v>falkirk-fc</v>
       </c>
       <c r="B504" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C504" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11378,7 +11378,7 @@
         <v>heart-of-midlothian-fc</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C505" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11395,7 +11395,7 @@
         <v>hibernian-fc</v>
       </c>
       <c r="B506" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C506" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11412,7 +11412,7 @@
         <v>kilmarnock-fc</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C507" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11429,7 +11429,7 @@
         <v>livingston-fc</v>
       </c>
       <c r="B508" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C508" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11446,7 +11446,7 @@
         <v>motherwell-fc</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C509" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11463,7 +11463,7 @@
         <v>rangers-fc</v>
       </c>
       <c r="B510" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C510" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11480,7 +11480,7 @@
         <v>st-mirren-fc</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C511" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11599,7 +11599,7 @@
         <v>elche-cf</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C518" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11667,7 +11667,7 @@
         <v>levante-ud</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C522" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11718,7 +11718,7 @@
         <v>real-oviedo</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C525" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11837,7 +11837,7 @@
         <v>albacete-balompie</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C532" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11854,7 +11854,7 @@
         <v>ud-almeria</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C533" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11871,7 +11871,7 @@
         <v>fc-andorra</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C534" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11888,7 +11888,7 @@
         <v>burgos-cf</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C535" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11905,7 +11905,7 @@
         <v>cadiz-cf</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C536" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11922,7 +11922,7 @@
         <v>cd-castellon</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C537" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11939,7 +11939,7 @@
         <v>ad-ceuta-fc</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C538" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11956,7 +11956,7 @@
         <v>cordoba-cf</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C539" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11973,7 +11973,7 @@
         <v>cultural-y-deportiva-leonesa</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C540" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11990,7 +11990,7 @@
         <v>sd-eibar</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C541" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12007,7 +12007,7 @@
         <v>sporting-de-gijon</v>
       </c>
       <c r="B542" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C542" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12024,7 +12024,7 @@
         <v>granada-cf</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C543" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12041,7 +12041,7 @@
         <v>sd-huesca</v>
       </c>
       <c r="B544" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C544" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12058,7 +12058,7 @@
         <v>deportivo-de-la-coruna</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C545" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12109,7 +12109,7 @@
         <v>malaga-cf</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C548" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12126,7 +12126,7 @@
         <v>cd-mirandes</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C549" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12143,7 +12143,7 @@
         <v>racing-de-santander</v>
       </c>
       <c r="B550" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C550" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12160,7 +12160,7 @@
         <v>real-sociedad-b</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C551" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12194,7 +12194,7 @@
         <v>real-zaragoza</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C553" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12211,7 +12211,7 @@
         <v>aik</v>
       </c>
       <c r="B554" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C554" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12228,7 +12228,7 @@
         <v>if-brommapojkarna</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C555" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12245,7 +12245,7 @@
         <v>degerfors-if</v>
       </c>
       <c r="B556" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C556" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12262,7 +12262,7 @@
         <v>djurgardens-if</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C557" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12279,7 +12279,7 @@
         <v>if-elfsborg</v>
       </c>
       <c r="B558" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C558" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12296,7 +12296,7 @@
         <v>gais</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C559" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12313,7 +12313,7 @@
         <v>ifk-goteborg</v>
       </c>
       <c r="B560" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C560" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12330,7 +12330,7 @@
         <v>bk-hacken</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C561" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12347,7 +12347,7 @@
         <v>halmstads-bk</v>
       </c>
       <c r="B562" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C562" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12364,7 +12364,7 @@
         <v>hammarby-if</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C563" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12381,7 +12381,7 @@
         <v>malmo-ff</v>
       </c>
       <c r="B564" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C564" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12398,7 +12398,7 @@
         <v>mjallby-aif</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C565" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12415,7 +12415,7 @@
         <v>ifk-norrkoping</v>
       </c>
       <c r="B566" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C566" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12432,7 +12432,7 @@
         <v>osters-if</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C567" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12449,7 +12449,7 @@
         <v>ik-sirius</v>
       </c>
       <c r="B568" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C568" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12466,7 +12466,7 @@
         <v>ifk-varnamo</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C569" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12483,7 +12483,7 @@
         <v>fc-basel</v>
       </c>
       <c r="B570" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C570" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12500,7 +12500,7 @@
         <v>grasshopper-club-zurich</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C571" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12517,7 +12517,7 @@
         <v>fc-lausanne-sport</v>
       </c>
       <c r="B572" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C572" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12534,7 +12534,7 @@
         <v>fc-lugano</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C573" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12551,7 +12551,7 @@
         <v>fc-luzern</v>
       </c>
       <c r="B574" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C574" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12568,7 +12568,7 @@
         <v>servette-fc</v>
       </c>
       <c r="B575" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C575" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12585,7 +12585,7 @@
         <v>fc-sion</v>
       </c>
       <c r="B576" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C576" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12602,7 +12602,7 @@
         <v>fc-st-gallen</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C577" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12619,7 +12619,7 @@
         <v>fc-thun</v>
       </c>
       <c r="B578" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C578" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12636,7 +12636,7 @@
         <v>fc-winterthur</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C579" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12653,7 +12653,7 @@
         <v>bsc-young-boys</v>
       </c>
       <c r="B580" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C580" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12670,7 +12670,7 @@
         <v>fc-zurich</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C581" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12687,7 +12687,7 @@
         <v>alanyaspor</v>
       </c>
       <c r="B582" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C582" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12704,7 +12704,7 @@
         <v>antalyaspor</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C583" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12721,7 +12721,7 @@
         <v>istanbul-basaksehir-fk</v>
       </c>
       <c r="B584" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C584" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12738,7 +12738,7 @@
         <v>besiktas-jk</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C585" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12755,7 +12755,7 @@
         <v>eyupspor</v>
       </c>
       <c r="B586" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C586" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12772,7 +12772,7 @@
         <v>fenerbahce-sk</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C587" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12789,7 +12789,7 @@
         <v>galatasaray-sk</v>
       </c>
       <c r="B588" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C588" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12806,7 +12806,7 @@
         <v>gaziantep-fk</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C589" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12823,7 +12823,7 @@
         <v>genclerbirligi-sk</v>
       </c>
       <c r="B590" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C590" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12840,7 +12840,7 @@
         <v>goztepe-sk</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C591" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12857,7 +12857,7 @@
         <v>fatih-karagumruk-sk</v>
       </c>
       <c r="B592" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C592" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12874,7 +12874,7 @@
         <v>kasimpasa-sk</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C593" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12891,7 +12891,7 @@
         <v>kayserispor</v>
       </c>
       <c r="B594" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C594" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12908,7 +12908,7 @@
         <v>kocaelispor</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C595" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12925,7 +12925,7 @@
         <v>konyaspor</v>
       </c>
       <c r="B596" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C596" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12942,7 +12942,7 @@
         <v>caykur-rizespor</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C597" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12959,7 +12959,7 @@
         <v>samsunspor</v>
       </c>
       <c r="B598" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C598" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12976,7 +12976,7 @@
         <v>trabzonspor</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C599" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12993,7 +12993,7 @@
         <v>atlanta-united-fc</v>
       </c>
       <c r="B600" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C600" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="D600" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
@@ -13010,7 +13010,7 @@
         <v>austin-fc</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C601" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="D601" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -13027,7 +13027,7 @@
         <v>club-de-foot-montreal</v>
       </c>
       <c r="B602" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C602" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="D602" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
@@ -13044,7 +13044,7 @@
         <v>charlotte-fc</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C603" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="D603" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
@@ -13061,7 +13061,7 @@
         <v>chicago-fire-fc</v>
       </c>
       <c r="B604" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C604" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="D604" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
@@ -13078,7 +13078,7 @@
         <v>fc-cincinnati</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C605" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="D605" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
@@ -13095,7 +13095,7 @@
         <v>colorado-rapids</v>
       </c>
       <c r="B606" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C606" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="D606" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
@@ -13112,7 +13112,7 @@
         <v>columbus-crew-sc</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C607" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="D607" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
@@ -13129,7 +13129,7 @@
         <v>dc-united</v>
       </c>
       <c r="B608" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C608" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="D608" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
@@ -13146,7 +13146,7 @@
         <v>fc-dallas</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C609" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="D609" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
@@ -13163,7 +13163,7 @@
         <v>houston-dynamo</v>
       </c>
       <c r="B610" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C610" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D610" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
@@ -13180,7 +13180,7 @@
         <v>inter-miami-cf</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C611" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="D611" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
@@ -13197,7 +13197,7 @@
         <v>los-angeles-fc</v>
       </c>
       <c r="B612" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C612" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13205,7 +13205,7 @@
       </c>
       <c r="D612" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
@@ -13214,7 +13214,7 @@
         <v>los-angeles-galaxy</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C613" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="D613" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
@@ -13231,7 +13231,7 @@
         <v>minnesota-united-fc</v>
       </c>
       <c r="B614" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C614" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="D614" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
@@ -13248,7 +13248,7 @@
         <v>nashville-sc</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C615" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="D615" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
@@ -13265,7 +13265,7 @@
         <v>new-england-revolution</v>
       </c>
       <c r="B616" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C616" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="D616" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
@@ -13282,7 +13282,7 @@
         <v>new-york-city-fc</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C617" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D617" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
@@ -13299,7 +13299,7 @@
         <v>new-york-red-bulls</v>
       </c>
       <c r="B618" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C618" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="D618" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
@@ -13316,7 +13316,7 @@
         <v>orlando-city-sc</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C619" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="D619" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
@@ -13333,7 +13333,7 @@
         <v>philadelphia-union</v>
       </c>
       <c r="B620" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C620" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="D620" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
@@ -13350,7 +13350,7 @@
         <v>portland-timbers</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C621" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="D621" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
@@ -13367,7 +13367,7 @@
         <v>real-salt-lake</v>
       </c>
       <c r="B622" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C622" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="D622" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
@@ -13384,7 +13384,7 @@
         <v>san-diego-fc</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C623" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="D623" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
@@ -13401,7 +13401,7 @@
         <v>san-jose-earthquakes</v>
       </c>
       <c r="B624" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C624" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="D624" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
@@ -13418,7 +13418,7 @@
         <v>seattle-sounders-fc</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C625" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="D625" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
@@ -13435,7 +13435,7 @@
         <v>sporting-kansas-city</v>
       </c>
       <c r="B626" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C626" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="D626" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
@@ -13452,7 +13452,7 @@
         <v>st-louis-city-sc</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C627" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="D627" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
@@ -13469,7 +13469,7 @@
         <v>toronto-fc</v>
       </c>
       <c r="B628" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C628" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="D628" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
@@ -13486,7 +13486,7 @@
         <v>vancouver-whitecaps-fc</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C629" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="D629" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
   </sheetData>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://v7hfx-my.sharepoint.com/personal/joseca20_v7hfx_onmicrosoft_com/Documents/web scraping/statsFutbol/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7F57AA5-B9DA-432F-9A57-20D620A8F3FB}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2FF4926-63D4-4718-9950-7B48CC613086}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="615">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -2060,10 +2060,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3030,12 +3026,14 @@
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="I22" s="10">
-        <v>46095</v>
-      </c>
-      <c r="J22" s="9"/>
+        <v>46090</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
@@ -9533,7 +9531,7 @@
       </c>
       <c r="D396" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
@@ -9550,7 +9548,7 @@
       </c>
       <c r="D397" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -9567,7 +9565,7 @@
       </c>
       <c r="D398" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
@@ -9584,7 +9582,7 @@
       </c>
       <c r="D399" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -9601,7 +9599,7 @@
       </c>
       <c r="D400" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
@@ -9618,7 +9616,7 @@
       </c>
       <c r="D401" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
@@ -9635,7 +9633,7 @@
       </c>
       <c r="D402" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
@@ -9652,7 +9650,7 @@
       </c>
       <c r="D403" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -9669,7 +9667,7 @@
       </c>
       <c r="D404" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
@@ -9686,7 +9684,7 @@
       </c>
       <c r="D405" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
@@ -9703,7 +9701,7 @@
       </c>
       <c r="D406" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -9720,7 +9718,7 @@
       </c>
       <c r="D407" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
@@ -9737,7 +9735,7 @@
       </c>
       <c r="D408" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -9754,7 +9752,7 @@
       </c>
       <c r="D409" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -9771,7 +9769,7 @@
       </c>
       <c r="D410" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -9788,7 +9786,7 @@
       </c>
       <c r="D411" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://v7hfx-my.sharepoint.com/personal/joseca20_v7hfx_onmicrosoft_com/Documents/web scraping/statsFutbol/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2FF4926-63D4-4718-9950-7B48CC613086}"/>
+  <xr:revisionPtr revIDLastSave="401" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE253722-373A-4654-BAF5-CC1988AAEB8C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -2060,6 +2060,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3026,10 +3030,10 @@
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="I22" s="10">
-        <v>46090</v>
+        <v>46095</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>599</v>
@@ -9531,7 +9535,7 @@
       </c>
       <c r="D396" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
@@ -9548,7 +9552,7 @@
       </c>
       <c r="D397" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -9565,7 +9569,7 @@
       </c>
       <c r="D398" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
@@ -9582,7 +9586,7 @@
       </c>
       <c r="D399" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -9599,7 +9603,7 @@
       </c>
       <c r="D400" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
@@ -9616,7 +9620,7 @@
       </c>
       <c r="D401" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
@@ -9633,7 +9637,7 @@
       </c>
       <c r="D402" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
@@ -9650,7 +9654,7 @@
       </c>
       <c r="D403" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -9667,7 +9671,7 @@
       </c>
       <c r="D404" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
@@ -9684,7 +9688,7 @@
       </c>
       <c r="D405" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
@@ -9701,7 +9705,7 @@
       </c>
       <c r="D406" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -9718,7 +9722,7 @@
       </c>
       <c r="D407" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
@@ -9735,7 +9739,7 @@
       </c>
       <c r="D408" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -9752,7 +9756,7 @@
       </c>
       <c r="D409" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -9769,7 +9773,7 @@
       </c>
       <c r="D410" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -9786,7 +9790,7 @@
       </c>
       <c r="D411" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://v7hfx-my.sharepoint.com/personal/joseca20_v7hfx_onmicrosoft_com/Documents/web scraping/statsFutbol/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="401" documentId="13_ncr:1_{C9A4DFC4-E548-46DD-BD70-6930DD5E65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE253722-373A-4654-BAF5-CC1988AAEB8C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FD02BD-A925-40E0-9F28-A49C351237C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="628">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -1452,18 +1452,9 @@
     <t>europe/sweden/mjallby-aif</t>
   </si>
   <si>
-    <t>europe/sweden/ifk-norrkoping</t>
-  </si>
-  <si>
-    <t>europe/sweden/osters-if</t>
-  </si>
-  <si>
     <t>europe/sweden/ik-sirius</t>
   </si>
   <si>
-    <t>europe/sweden/ifk-varnamo</t>
-  </si>
-  <si>
     <t>europe/switzerland/fc-basel</t>
   </si>
   <si>
@@ -1500,60 +1491,6 @@
     <t>europe/switzerland/fc-zurich</t>
   </si>
   <si>
-    <t>europe/turkey/alanyaspor</t>
-  </si>
-  <si>
-    <t>europe/turkey/antalyaspor</t>
-  </si>
-  <si>
-    <t>europe/turkey/istanbul-basaksehir-fk</t>
-  </si>
-  <si>
-    <t>europe/turkey/besiktas-jk</t>
-  </si>
-  <si>
-    <t>europe/turkey/eyupspor</t>
-  </si>
-  <si>
-    <t>europe/turkey/fenerbahce-sk</t>
-  </si>
-  <si>
-    <t>europe/turkey/galatasaray-sk</t>
-  </si>
-  <si>
-    <t>europe/turkey/gaziantep-fk</t>
-  </si>
-  <si>
-    <t>europe/turkey/genclerbirligi-sk</t>
-  </si>
-  <si>
-    <t>europe/turkey/goztepe-sk</t>
-  </si>
-  <si>
-    <t>europe/turkey/fatih-karagumruk-sk</t>
-  </si>
-  <si>
-    <t>europe/turkey/kasimpasa-sk</t>
-  </si>
-  <si>
-    <t>europe/turkey/kayserispor</t>
-  </si>
-  <si>
-    <t>europe/turkey/kocaelispor</t>
-  </si>
-  <si>
-    <t>europe/turkey/konyaspor</t>
-  </si>
-  <si>
-    <t>europe/turkey/caykur-rizespor</t>
-  </si>
-  <si>
-    <t>europe/turkey/samsunspor</t>
-  </si>
-  <si>
-    <t>europe/turkey/trabzonspor</t>
-  </si>
-  <si>
     <t>n-s-america/usa/atlanta-united-fc</t>
   </si>
   <si>
@@ -1821,9 +1758,6 @@
     <t>europe/finland/if-gnistan</t>
   </si>
   <si>
-    <t>europe/finland/fc-haka</t>
-  </si>
-  <si>
     <t>europe/finland/hjk-helsinki</t>
   </si>
   <si>
@@ -1836,9 +1770,6 @@
     <t>europe/finland/ff-jaro</t>
   </si>
   <si>
-    <t>europe/finland/kotkan-tyovaen-palloilijat</t>
-  </si>
-  <si>
     <t>europe/finland/kuopion-palloseura</t>
   </si>
   <si>
@@ -1903,6 +1834,114 @@
   </si>
   <si>
     <t>n-s-america/argentina/club-gimnasia-de-mendoza</t>
+  </si>
+  <si>
+    <t>europe/sweden/kalmar-ff</t>
+  </si>
+  <si>
+    <t>europe/sweden/orgryte-is</t>
+  </si>
+  <si>
+    <t>europe/sweden/vasteras-sk</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/bohemians-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/derry-city-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/drogheda-united-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/dundalk-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/galway-united-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/shamrock-rovers-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/shelbourne-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/sligo-rovers-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/st-patricks-athletic-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/ireland/waterford-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/al-ahly-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/al-ittihad-ac</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/al-masry-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/arab-contractors-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/ceramica-cleopatra-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/talaea-el-gaish-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/el-gouna-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/enppi-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/ghazi-el-mahalla-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/haras-el-hodoud-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/ismaily-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/kahrabaa-ismailia-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/modern-sport-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/national-bank-of-egypt-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/petrojet-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/pharco-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/pyramids-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/smouha-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/wadi-degla-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/zamalek-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/zed-fc</t>
+  </si>
+  <si>
+    <t>europe/finland/fc-lahti</t>
+  </si>
+  <si>
+    <t>europe/finland/tps-turku</t>
   </si>
 </sst>
 </file>
@@ -1998,7 +2037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2017,6 +2056,10 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2062,15 +2105,11 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:D629" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D629" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C629">
-    <sortCondition ref="C1:C629"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:D642" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D642" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C611">
+    <sortCondition ref="C1:C611"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="3">
@@ -2385,7 +2424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3E121-4DD2-4C5A-A60B-ED62DD98B116}">
-  <dimension ref="A1:J629"/>
+  <dimension ref="A1:J642"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -2407,7 +2446,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2427,7 +2466,7 @@
         <v>SI</v>
       </c>
       <c r="G2" s="9" t="str" cm="1">
-        <f t="array" ref="G2:G33">_xlfn.UNIQUE(Tabla1[PAIS])</f>
+        <f t="array" ref="G2:G34">_xlfn.UNIQUE(Tabla1[PAIS])</f>
         <v>argentina</v>
       </c>
       <c r="H2" s="9" t="str">
@@ -2438,7 +2477,7 @@
         <v>46044</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2468,7 +2507,7 @@
         <v>46030</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2491,14 +2530,14 @@
         <v>austria</v>
       </c>
       <c r="H4" s="9" t="str">
-        <f t="shared" ref="H4:H33" ca="1" si="0">IF(I4&gt;TODAY(),"","X")</f>
+        <f t="shared" ref="H4:H35" ca="1" si="0">IF(I4&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="I4" s="10">
         <v>46059</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2528,7 +2567,7 @@
         <v>46038</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2558,7 +2597,7 @@
         <v>46050</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2582,13 +2621,13 @@
       </c>
       <c r="H7" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="I7" s="10">
-        <v>46060</v>
+        <v>46387</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2618,7 +2657,7 @@
         <v>46052</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2648,7 +2687,7 @@
         <v>46039</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2678,7 +2717,7 @@
         <v>46045</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2708,7 +2747,7 @@
         <v>46053</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2738,7 +2777,7 @@
         <v>46059</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2747,7 +2786,7 @@
         <v>estudiantes-de-rio-cuarto</v>
       </c>
       <c r="B13" t="s">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2768,7 +2807,7 @@
         <v>46073</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2798,7 +2837,7 @@
         <v>46030</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2807,7 +2846,7 @@
         <v>club-gimnasia-de-mendoza</v>
       </c>
       <c r="B15" t="s">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2822,12 +2861,14 @@
       </c>
       <c r="H15" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="I15" s="10">
         <v>46116</v>
       </c>
-      <c r="J15" s="9"/>
+      <c r="J15" s="9" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
@@ -2856,7 +2897,7 @@
         <v>46030</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -2886,7 +2927,7 @@
         <v>46030</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -2916,7 +2957,7 @@
         <v>46030</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -2946,7 +2987,7 @@
         <v>46030</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -2976,7 +3017,7 @@
         <v>46031</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -3006,7 +3047,7 @@
         <v>46030</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -3030,13 +3071,13 @@
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="I22" s="10">
         <v>46095</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -3066,7 +3107,7 @@
         <v>46052</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -3096,7 +3137,7 @@
         <v>46052</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -3126,7 +3167,7 @@
         <v>46030</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -3156,7 +3197,7 @@
         <v>46038</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -3186,7 +3227,7 @@
         <v>46030</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -3216,7 +3257,7 @@
         <v>46030</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -3246,7 +3287,7 @@
         <v>46030</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -3270,12 +3311,14 @@
       </c>
       <c r="H30" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="I30" s="10">
         <v>46117</v>
       </c>
-      <c r="J30" s="9"/>
+      <c r="J30" s="9" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
@@ -3304,7 +3347,7 @@
         <v>46036</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -3313,7 +3356,7 @@
         <v>adelaide-united-fc</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3324,17 +3367,17 @@
         <v>SI</v>
       </c>
       <c r="G32" s="9" t="str">
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="H32" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>X</v>
       </c>
       <c r="I32" s="10">
-        <v>46039</v>
+        <v>46074</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -3343,7 +3386,7 @@
         <v>auckland-fc</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3354,17 +3397,17 @@
         <v>SI</v>
       </c>
       <c r="G33" s="9" t="str">
-        <v>usa</v>
+        <v>ireland</v>
       </c>
       <c r="H33" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>X</v>
       </c>
       <c r="I33" s="10">
-        <v>46074</v>
+        <v>46121</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -3373,15 +3416,28 @@
         <v>brisbane-roar-fc</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C34" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D34" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="G34" s="9" t="str">
+        <v>egypt</v>
+      </c>
+      <c r="H34" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="I34" s="10">
+        <v>46121</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>576</v>
-      </c>
-      <c r="C34" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D34" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -3390,7 +3446,7 @@
         <v>central-coast-mariners-fc</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3400,6 +3456,10 @@
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="9"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
@@ -3407,7 +3467,7 @@
         <v>macarthur-fc</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3424,7 +3484,7 @@
         <v>melbourne-city-fc</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3441,7 +3501,7 @@
         <v>melbourne-victory-fc</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3458,7 +3518,7 @@
         <v>newcastle-jets-fc</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3475,7 +3535,7 @@
         <v>perth-glory-fc</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="C40" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3492,7 +3552,7 @@
         <v>sydney-fc</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3509,7 +3569,7 @@
         <v>wellington-phoenix-fc</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3526,7 +3586,7 @@
         <v>western-sydney-wanderers-fc</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4019,7 +4079,7 @@
         <v>club-athletico-paranaense</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="C72" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4104,7 +4164,7 @@
         <v>associacao-chapecoense-de-futebol</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="C77" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4138,7 +4198,7 @@
         <v>coritiba-football-club</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="C79" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4274,7 +4334,7 @@
         <v>clube-do-remo</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="C87" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4367,7 +4427,7 @@
       </c>
       <c r="D92" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -4384,7 +4444,7 @@
       </c>
       <c r="D93" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -4401,7 +4461,7 @@
       </c>
       <c r="D94" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -4418,7 +4478,7 @@
       </c>
       <c r="D95" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -4435,7 +4495,7 @@
       </c>
       <c r="D96" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -4452,7 +4512,7 @@
       </c>
       <c r="D97" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -4469,7 +4529,7 @@
       </c>
       <c r="D98" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -4486,7 +4546,7 @@
       </c>
       <c r="D99" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -4503,7 +4563,7 @@
       </c>
       <c r="D100" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -4520,7 +4580,7 @@
       </c>
       <c r="D101" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -4537,7 +4597,7 @@
       </c>
       <c r="D102" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -4554,7 +4614,7 @@
       </c>
       <c r="D103" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -4571,7 +4631,7 @@
       </c>
       <c r="D104" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -4588,7 +4648,7 @@
       </c>
       <c r="D105" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -4605,7 +4665,7 @@
       </c>
       <c r="D106" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -4622,7 +4682,7 @@
       </c>
       <c r="D107" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -4699,7 +4759,7 @@
         <v>deportes-concepcion</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>607</v>
+        <v>584</v>
       </c>
       <c r="C112" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4886,7 +4946,7 @@
         <v>cd-universidad-de-concepcion</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="C123" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5005,7 +5065,7 @@
         <v>cucuta-deportivo-fc</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="C130" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5073,7 +5133,7 @@
         <v>internacional-de-bogota</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="C134" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5090,7 +5150,7 @@
         <v>jaguares-de-cordoba</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="C135" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5889,7 +5949,7 @@
         <v>sd-aucas</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="C182" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5906,7 +5966,7 @@
         <v>barcelona-sc</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="C183" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5923,7 +5983,7 @@
         <v>delfin-sc</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="C184" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5940,7 +6000,7 @@
         <v>cd-cuenca</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5957,7 +6017,7 @@
         <v>cs-emelec</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5974,7 +6034,7 @@
         <v>guayaquil-city-fc</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="C187" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5991,7 +6051,7 @@
         <v>csd-independiente-del-valle</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="C188" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6008,7 +6068,7 @@
         <v>ldu-quito</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="C189" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6025,7 +6085,7 @@
         <v>leones-fc</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="C190" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6042,7 +6102,7 @@
         <v>libertad-fc</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="C191" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6059,7 +6119,7 @@
         <v>csd-macara</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="C192" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6076,7 +6136,7 @@
         <v>manta-fc</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="C193" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6093,7 +6153,7 @@
         <v>mushuc-runa-sc</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="C194" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6110,7 +6170,7 @@
         <v>orense-sc</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="C195" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6127,7 +6187,7 @@
         <v>tecnico-universitario</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="C196" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6144,7 +6204,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="C197" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6909,7 +6969,7 @@
         <v>if-gnistan</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6917,16 +6977,16 @@
       </c>
       <c r="D242" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-haka</v>
+        <v>hjk-helsinki</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6934,16 +6994,16 @@
       </c>
       <c r="D243" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hjk-helsinki</v>
+        <v>fc-ilves</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6951,16 +7011,16 @@
       </c>
       <c r="D244" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-ilves</v>
+        <v>fc-inter-turku</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="C245" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6968,16 +7028,16 @@
       </c>
       <c r="D245" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-inter-turku</v>
+        <v>ff-jaro</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="C246" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6985,16 +7045,16 @@
       </c>
       <c r="D246" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ff-jaro</v>
+        <v>kuopion-palloseura</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="C247" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7002,16 +7062,16 @@
       </c>
       <c r="D247" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kotkan-tyovaen-palloilijat</v>
+        <v>fc-lahti</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>592</v>
+        <v>626</v>
       </c>
       <c r="C248" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7019,16 +7079,16 @@
       </c>
       <c r="D248" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kuopion-palloseura</v>
+        <v>ifk-mariehamn</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7036,16 +7096,16 @@
       </c>
       <c r="D249" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ifk-mariehamn</v>
+        <v>ac-oulu</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7053,16 +7113,16 @@
       </c>
       <c r="D250" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-oulu</v>
+        <v>sjk</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7070,16 +7130,16 @@
       </c>
       <c r="D251" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sjk</v>
+        <v>tps-turku</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="C252" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7087,7 +7147,7 @@
       </c>
       <c r="D252" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -7096,7 +7156,7 @@
         <v>vaasan-palloseura</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="C253" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7104,7 +7164,7 @@
       </c>
       <c r="D253" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -7215,7 +7275,7 @@
         <v>fc-lorient</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="C260" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7266,7 +7326,7 @@
         <v>fc-metz</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="C263" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7334,7 +7394,7 @@
         <v>paris-fc</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="C267" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7793,7 +7853,7 @@
         <v>fc-koln</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="C294" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7844,7 +7904,7 @@
         <v>hamburger-sv</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C297" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8337,7 +8397,7 @@
         <v>aek-athens-fc</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="C326" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8354,7 +8414,7 @@
         <v>ael-fc</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="C327" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8371,7 +8431,7 @@
         <v>aris-thessaloniki-fc</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="C328" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8388,7 +8448,7 @@
         <v>asteras-tripolis-fc</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8405,7 +8465,7 @@
         <v>atromitos-fc</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="C330" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8422,7 +8482,7 @@
         <v>ae-kifisia-fc</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="C331" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8439,7 +8499,7 @@
         <v>levadiakos-fc</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="C332" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8456,7 +8516,7 @@
         <v>ofi-crete-fc</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="C333" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8473,7 +8533,7 @@
         <v>olympiacos-fc</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="C334" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8490,7 +8550,7 @@
         <v>panathinaikos-fc</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="C335" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8507,7 +8567,7 @@
         <v>panetolikos-fc</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="C336" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8524,7 +8584,7 @@
         <v>panserraikos-fc</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="C337" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8541,7 +8601,7 @@
         <v>paok-fc</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="C338" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8558,7 +8618,7 @@
         <v>volos-fc</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="C339" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8677,7 +8737,7 @@
         <v>us-cremonese</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="C346" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8830,7 +8890,7 @@
         <v>ac-pisa-1909</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="C355" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8847,7 +8907,7 @@
         <v>us-sassuolo-calcio</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="C356" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9535,7 +9595,7 @@
       </c>
       <c r="D396" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
@@ -9552,7 +9612,7 @@
       </c>
       <c r="D397" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -9569,7 +9629,7 @@
       </c>
       <c r="D398" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
@@ -9586,7 +9646,7 @@
       </c>
       <c r="D399" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -9603,7 +9663,7 @@
       </c>
       <c r="D400" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
@@ -9620,7 +9680,7 @@
       </c>
       <c r="D401" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
@@ -9637,7 +9697,7 @@
       </c>
       <c r="D402" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
@@ -9654,7 +9714,7 @@
       </c>
       <c r="D403" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -9671,7 +9731,7 @@
       </c>
       <c r="D404" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
@@ -9688,7 +9748,7 @@
       </c>
       <c r="D405" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
@@ -9705,7 +9765,7 @@
       </c>
       <c r="D406" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -9722,7 +9782,7 @@
       </c>
       <c r="D407" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
@@ -9739,7 +9799,7 @@
       </c>
       <c r="D408" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -9756,7 +9816,7 @@
       </c>
       <c r="D409" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -9773,7 +9833,7 @@
       </c>
       <c r="D410" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -9790,7 +9850,7 @@
       </c>
       <c r="D411" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
@@ -9935,7 +9995,7 @@
         <v>fc-cajamarca</v>
       </c>
       <c r="B420" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="C420" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10037,7 +10097,7 @@
         <v>club-deportivo-moquegua</v>
       </c>
       <c r="B426" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="C426" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11023,7 +11083,7 @@
         <v>al-hazem-fc</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="C484" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11074,7 +11134,7 @@
         <v>al-najma-sc</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="C487" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11278,7 +11338,7 @@
         <v>neom-sc</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="C499" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11601,7 +11661,7 @@
         <v>elche-cf</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="C518" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11669,7 +11729,7 @@
         <v>levante-ud</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="C522" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11720,7 +11780,7 @@
         <v>real-oviedo</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="C525" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11873,7 +11933,7 @@
         <v>fc-andorra</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="C534" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11941,7 +12001,7 @@
         <v>ad-ceuta-fc</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="C538" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11975,7 +12035,7 @@
         <v>cultural-y-deportiva-leonesa</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="C540" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12162,7 +12222,7 @@
         <v>real-sociedad-b</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="C551" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12221,7 +12281,7 @@
       </c>
       <c r="D554" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.3">
@@ -12238,7 +12298,7 @@
       </c>
       <c r="D555" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
@@ -12255,7 +12315,7 @@
       </c>
       <c r="D556" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.3">
@@ -12272,7 +12332,7 @@
       </c>
       <c r="D557" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.3">
@@ -12289,7 +12349,7 @@
       </c>
       <c r="D558" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
@@ -12306,7 +12366,7 @@
       </c>
       <c r="D559" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
@@ -12323,7 +12383,7 @@
       </c>
       <c r="D560" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.3">
@@ -12340,7 +12400,7 @@
       </c>
       <c r="D561" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.3">
@@ -12357,7 +12417,7 @@
       </c>
       <c r="D562" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.3">
@@ -12374,16 +12434,16 @@
       </c>
       <c r="D563" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>malmo-ff</v>
+        <v>kalmar-ff</v>
       </c>
       <c r="B564" s="5" t="s">
-        <v>462</v>
+        <v>592</v>
       </c>
       <c r="C564" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12391,16 +12451,16 @@
       </c>
       <c r="D564" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mjallby-aif</v>
+        <v>malmo-ff</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C565" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12408,16 +12468,16 @@
       </c>
       <c r="D565" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ifk-norrkoping</v>
+        <v>mjallby-aif</v>
       </c>
       <c r="B566" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C566" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12425,16 +12485,16 @@
       </c>
       <c r="D566" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>osters-if</v>
+        <v>orgryte-is</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>465</v>
+        <v>593</v>
       </c>
       <c r="C567" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12442,7 +12502,7 @@
       </c>
       <c r="D567" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
@@ -12451,7 +12511,7 @@
         <v>ik-sirius</v>
       </c>
       <c r="B568" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C568" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12459,16 +12519,16 @@
       </c>
       <c r="D568" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ifk-varnamo</v>
+        <v>vasteras-sk</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>467</v>
+        <v>594</v>
       </c>
       <c r="C569" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12476,7 +12536,7 @@
       </c>
       <c r="D569" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.3">
@@ -12485,7 +12545,7 @@
         <v>fc-basel</v>
       </c>
       <c r="B570" s="5" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C570" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12502,7 +12562,7 @@
         <v>grasshopper-club-zurich</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C571" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12519,7 +12579,7 @@
         <v>fc-lausanne-sport</v>
       </c>
       <c r="B572" s="5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C572" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12536,7 +12596,7 @@
         <v>fc-lugano</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C573" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12553,7 +12613,7 @@
         <v>fc-luzern</v>
       </c>
       <c r="B574" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C574" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12570,7 +12630,7 @@
         <v>servette-fc</v>
       </c>
       <c r="B575" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C575" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12587,7 +12647,7 @@
         <v>fc-sion</v>
       </c>
       <c r="B576" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C576" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12604,7 +12664,7 @@
         <v>fc-st-gallen</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C577" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12621,7 +12681,7 @@
         <v>fc-thun</v>
       </c>
       <c r="B578" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C578" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12638,7 +12698,7 @@
         <v>fc-winterthur</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C579" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12655,7 +12715,7 @@
         <v>bsc-young-boys</v>
       </c>
       <c r="B580" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C580" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12672,7 +12732,7 @@
         <v>fc-zurich</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C581" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12686,14 +12746,14 @@
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A582" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>alanyaspor</v>
+        <v>atlanta-united-fc</v>
       </c>
       <c r="B582" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C582" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D582" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12703,14 +12763,14 @@
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A583" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>antalyaspor</v>
+        <v>austin-fc</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C583" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D583" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12720,14 +12780,14 @@
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>istanbul-basaksehir-fk</v>
+        <v>club-de-foot-montreal</v>
       </c>
       <c r="B584" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C584" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D584" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12737,14 +12797,14 @@
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A585" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>besiktas-jk</v>
+        <v>charlotte-fc</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C585" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D585" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12754,14 +12814,14 @@
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A586" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>eyupspor</v>
+        <v>chicago-fire-fc</v>
       </c>
       <c r="B586" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C586" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D586" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12771,14 +12831,14 @@
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A587" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fenerbahce-sk</v>
+        <v>fc-cincinnati</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C587" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D587" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12788,14 +12848,14 @@
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A588" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>galatasaray-sk</v>
+        <v>colorado-rapids</v>
       </c>
       <c r="B588" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C588" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D588" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12805,14 +12865,14 @@
     <row r="589" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A589" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gaziantep-fk</v>
+        <v>columbus-crew-sc</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C589" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D589" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12822,14 +12882,14 @@
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>genclerbirligi-sk</v>
+        <v>dc-united</v>
       </c>
       <c r="B590" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C590" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D590" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12839,14 +12899,14 @@
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A591" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>goztepe-sk</v>
+        <v>fc-dallas</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C591" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D591" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12856,14 +12916,14 @@
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A592" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fatih-karagumruk-sk</v>
+        <v>houston-dynamo</v>
       </c>
       <c r="B592" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C592" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D592" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12873,14 +12933,14 @@
     <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kasimpasa-sk</v>
+        <v>inter-miami-cf</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C593" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D593" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12890,14 +12950,14 @@
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kayserispor</v>
+        <v>los-angeles-fc</v>
       </c>
       <c r="B594" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C594" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D594" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12907,14 +12967,14 @@
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kocaelispor</v>
+        <v>los-angeles-galaxy</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C595" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D595" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12924,14 +12984,14 @@
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>konyaspor</v>
+        <v>minnesota-united-fc</v>
       </c>
       <c r="B596" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C596" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D596" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12941,14 +13001,14 @@
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>caykur-rizespor</v>
+        <v>nashville-sc</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C597" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D597" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12958,14 +13018,14 @@
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>samsunspor</v>
+        <v>new-england-revolution</v>
       </c>
       <c r="B598" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C598" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D598" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12975,14 +13035,14 @@
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>trabzonspor</v>
+        <v>new-york-city-fc</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C599" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>turkey</v>
+        <v>usa</v>
       </c>
       <c r="D599" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
@@ -12992,10 +13052,10 @@
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atlanta-united-fc</v>
+        <v>new-york-red-bulls</v>
       </c>
       <c r="B600" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C600" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13009,10 +13069,10 @@
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>austin-fc</v>
+        <v>orlando-city-sc</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C601" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13026,10 +13086,10 @@
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-de-foot-montreal</v>
+        <v>philadelphia-union</v>
       </c>
       <c r="B602" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C602" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13043,10 +13103,10 @@
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>charlotte-fc</v>
+        <v>portland-timbers</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C603" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13060,10 +13120,10 @@
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chicago-fire-fc</v>
+        <v>real-salt-lake</v>
       </c>
       <c r="B604" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C604" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13077,10 +13137,10 @@
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-cincinnati</v>
+        <v>san-diego-fc</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C605" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13094,10 +13154,10 @@
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>colorado-rapids</v>
+        <v>san-jose-earthquakes</v>
       </c>
       <c r="B606" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C606" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13111,10 +13171,10 @@
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>columbus-crew-sc</v>
+        <v>seattle-sounders-fc</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C607" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13128,10 +13188,10 @@
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dc-united</v>
+        <v>sporting-kansas-city</v>
       </c>
       <c r="B608" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C608" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13145,10 +13205,10 @@
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-dallas</v>
+        <v>st-louis-city-sc</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C609" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13162,10 +13222,10 @@
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>houston-dynamo</v>
+        <v>toronto-fc</v>
       </c>
       <c r="B610" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C610" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13179,10 +13239,10 @@
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>inter-miami-cf</v>
+        <v>vancouver-whitecaps-fc</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C611" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13194,313 +13254,534 @@
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A612" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>los-angeles-fc</v>
+      <c r="A612" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>bohemians-fc</v>
       </c>
       <c r="B612" t="s">
-        <v>510</v>
-      </c>
-      <c r="C612" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D612" s="8" t="str">
+        <v>595</v>
+      </c>
+      <c r="C612" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D612" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A613" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>los-angeles-galaxy</v>
-      </c>
-      <c r="B613" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="C613" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D613" s="8" t="str">
+      <c r="A613" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>derry-city-fc</v>
+      </c>
+      <c r="B613" t="s">
+        <v>596</v>
+      </c>
+      <c r="C613" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D613" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A614" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>minnesota-united-fc</v>
+      <c r="A614" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>drogheda-united-fc</v>
       </c>
       <c r="B614" t="s">
-        <v>512</v>
-      </c>
-      <c r="C614" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D614" s="8" t="str">
+        <v>597</v>
+      </c>
+      <c r="C614" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D614" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A615" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nashville-sc</v>
-      </c>
-      <c r="B615" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="C615" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D615" s="8" t="str">
+      <c r="A615" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>dundalk-fc</v>
+      </c>
+      <c r="B615" t="s">
+        <v>598</v>
+      </c>
+      <c r="C615" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D615" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A616" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>new-england-revolution</v>
+      <c r="A616" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>galway-united-fc</v>
       </c>
       <c r="B616" t="s">
-        <v>514</v>
-      </c>
-      <c r="C616" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D616" s="8" t="str">
+        <v>599</v>
+      </c>
+      <c r="C616" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D616" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A617" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>new-york-city-fc</v>
-      </c>
-      <c r="B617" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="C617" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D617" s="8" t="str">
+      <c r="A617" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shamrock-rovers-fc</v>
+      </c>
+      <c r="B617" t="s">
+        <v>600</v>
+      </c>
+      <c r="C617" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D617" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A618" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>new-york-red-bulls</v>
+      <c r="A618" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shelbourne-fc</v>
       </c>
       <c r="B618" t="s">
-        <v>516</v>
-      </c>
-      <c r="C618" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D618" s="8" t="str">
+        <v>601</v>
+      </c>
+      <c r="C618" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D618" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A619" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>orlando-city-sc</v>
-      </c>
-      <c r="B619" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="C619" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D619" s="8" t="str">
+      <c r="A619" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>sligo-rovers-fc</v>
+      </c>
+      <c r="B619" t="s">
+        <v>602</v>
+      </c>
+      <c r="C619" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D619" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A620" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>philadelphia-union</v>
+      <c r="A620" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>st-patricks-athletic-fc</v>
       </c>
       <c r="B620" t="s">
-        <v>518</v>
-      </c>
-      <c r="C620" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D620" s="8" t="str">
+        <v>603</v>
+      </c>
+      <c r="C620" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D620" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A621" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>portland-timbers</v>
-      </c>
-      <c r="B621" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="C621" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D621" s="8" t="str">
+      <c r="A621" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>waterford-fc</v>
+      </c>
+      <c r="B621" t="s">
+        <v>604</v>
+      </c>
+      <c r="C621" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ireland</v>
+      </c>
+      <c r="D621" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A622" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-salt-lake</v>
+      <c r="A622" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>al-ahly-sc</v>
       </c>
       <c r="B622" t="s">
-        <v>520</v>
-      </c>
-      <c r="C622" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D622" s="8" t="str">
+        <v>605</v>
+      </c>
+      <c r="C622" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D622" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A623" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>san-diego-fc</v>
-      </c>
-      <c r="B623" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="C623" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D623" s="8" t="str">
+      <c r="A623" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>al-ittihad-ac</v>
+      </c>
+      <c r="B623" t="s">
+        <v>606</v>
+      </c>
+      <c r="C623" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D623" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A624" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>san-jose-earthquakes</v>
+      <c r="A624" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>al-masry-sc</v>
       </c>
       <c r="B624" t="s">
-        <v>522</v>
-      </c>
-      <c r="C624" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D624" s="8" t="str">
+        <v>607</v>
+      </c>
+      <c r="C624" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D624" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A625" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>seattle-sounders-fc</v>
-      </c>
-      <c r="B625" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="C625" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D625" s="8" t="str">
+      <c r="A625" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>arab-contractors-sc</v>
+      </c>
+      <c r="B625" t="s">
+        <v>608</v>
+      </c>
+      <c r="C625" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D625" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A626" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-kansas-city</v>
+      <c r="A626" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ceramica-cleopatra-fc</v>
       </c>
       <c r="B626" t="s">
-        <v>524</v>
-      </c>
-      <c r="C626" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D626" s="8" t="str">
+        <v>609</v>
+      </c>
+      <c r="C626" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D626" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A627" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>st-louis-city-sc</v>
-      </c>
-      <c r="B627" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="C627" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D627" s="8" t="str">
+      <c r="A627" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>talaea-el-gaish-sc</v>
+      </c>
+      <c r="B627" t="s">
+        <v>610</v>
+      </c>
+      <c r="C627" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D627" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A628" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>toronto-fc</v>
+      <c r="A628" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>el-gouna-fc</v>
       </c>
       <c r="B628" t="s">
-        <v>526</v>
-      </c>
-      <c r="C628" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D628" s="8" t="str">
+        <v>611</v>
+      </c>
+      <c r="C628" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D628" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A629" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vancouver-whitecaps-fc</v>
-      </c>
-      <c r="B629" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="C629" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
-      </c>
-      <c r="D629" s="8" t="str">
+      <c r="A629" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>enppi-sc</v>
+      </c>
+      <c r="B629" t="s">
+        <v>612</v>
+      </c>
+      <c r="C629" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D629" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A630" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ghazi-el-mahalla-sc</v>
+      </c>
+      <c r="B630" t="s">
+        <v>613</v>
+      </c>
+      <c r="C630" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D630" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A631" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>haras-el-hodoud-sc</v>
+      </c>
+      <c r="B631" t="s">
+        <v>614</v>
+      </c>
+      <c r="C631" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D631" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A632" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ismaily-sc</v>
+      </c>
+      <c r="B632" t="s">
+        <v>615</v>
+      </c>
+      <c r="C632" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D632" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A633" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kahrabaa-ismailia-sc</v>
+      </c>
+      <c r="B633" t="s">
+        <v>616</v>
+      </c>
+      <c r="C633" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D633" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A634" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>modern-sport-fc</v>
+      </c>
+      <c r="B634" t="s">
+        <v>617</v>
+      </c>
+      <c r="C634" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D634" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A635" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>national-bank-of-egypt-sc</v>
+      </c>
+      <c r="B635" t="s">
+        <v>618</v>
+      </c>
+      <c r="C635" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D635" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A636" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>petrojet-sc</v>
+      </c>
+      <c r="B636" t="s">
+        <v>619</v>
+      </c>
+      <c r="C636" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D636" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A637" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>pharco-fc</v>
+      </c>
+      <c r="B637" t="s">
+        <v>620</v>
+      </c>
+      <c r="C637" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D637" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A638" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>pyramids-fc</v>
+      </c>
+      <c r="B638" t="s">
+        <v>621</v>
+      </c>
+      <c r="C638" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D638" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A639" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>smouha-sc</v>
+      </c>
+      <c r="B639" t="s">
+        <v>622</v>
+      </c>
+      <c r="C639" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D639" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A640" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>wadi-degla-sc</v>
+      </c>
+      <c r="B640" t="s">
+        <v>623</v>
+      </c>
+      <c r="C640" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D640" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A641" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>zamalek-sc</v>
+      </c>
+      <c r="B641" t="s">
+        <v>624</v>
+      </c>
+      <c r="C641" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D641" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A642" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>zed-fc</v>
+      </c>
+      <c r="B642" t="s">
+        <v>625</v>
+      </c>
+      <c r="C642" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>egypt</v>
+      </c>
+      <c r="D642" s="12" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$G$2:$H$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J33">
+  <conditionalFormatting sqref="J2:J35">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="act">
       <formula>NOT(ISERROR(SEARCH("act",J2)))</formula>
     </cfRule>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A8982B-6812-4F9B-8430-8AEC7E4ACAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82333529-FA44-45DF-996F-B604E89676C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="629">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E2" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H2" s="9" t="str" cm="1">
         <f t="array" ref="H2:H34">_xlfn.UNIQUE(Tabla1[PAIS])</f>
@@ -2484,12 +2484,14 @@
       </c>
       <c r="I2" s="9" t="str">
         <f ca="1">IF(J2&gt;TODAY(),"","X")</f>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J2" s="10">
         <v>46227</v>
       </c>
-      <c r="K2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
@@ -2509,7 +2511,7 @@
       </c>
       <c r="E3" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H3" s="9" t="str">
         <v>australia</v>
@@ -2541,7 +2543,7 @@
       </c>
       <c r="E4" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H4" s="9" t="str">
         <v>austria</v>
@@ -2575,7 +2577,7 @@
       </c>
       <c r="E5" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H5" s="9" t="str">
         <v>belgium</v>
@@ -2607,7 +2609,7 @@
       </c>
       <c r="E6" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H6" s="9" t="str">
         <v>brazil</v>
@@ -2641,14 +2643,14 @@
       </c>
       <c r="E7" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H7" s="9" t="str">
         <v>bulgaria</v>
       </c>
       <c r="I7" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J7" s="10">
         <v>46224</v>
@@ -2675,7 +2677,7 @@
       </c>
       <c r="E8" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H8" s="9" t="str">
         <v>chile</v>
@@ -2709,7 +2711,7 @@
       </c>
       <c r="E9" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H9" s="9" t="str">
         <v>colombia</v>
@@ -2741,7 +2743,7 @@
       </c>
       <c r="E10" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H10" s="9" t="str">
         <v>croatia</v>
@@ -2775,7 +2777,7 @@
       </c>
       <c r="E11" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H11" s="9" t="str">
         <v>czech-republic</v>
@@ -2809,7 +2811,7 @@
       </c>
       <c r="E12" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H12" s="9" t="str">
         <v>denmark</v>
@@ -2843,7 +2845,7 @@
       </c>
       <c r="E13" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H13" s="9" t="str">
         <v>ecuador</v>
@@ -2877,7 +2879,7 @@
       </c>
       <c r="E14" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H14" s="9" t="str">
         <v>england</v>
@@ -2909,7 +2911,7 @@
       </c>
       <c r="E15" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H15" s="9" t="str">
         <v>finland</v>
@@ -2943,7 +2945,7 @@
       </c>
       <c r="E16" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H16" s="9" t="str">
         <v>france</v>
@@ -2975,7 +2977,7 @@
       </c>
       <c r="E17" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H17" s="9" t="str">
         <v>germany</v>
@@ -3007,7 +3009,7 @@
       </c>
       <c r="E18" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H18" s="9" t="str">
         <v>greece</v>
@@ -3039,7 +3041,7 @@
       </c>
       <c r="E19" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H19" s="9" t="str">
         <v>italy</v>
@@ -3071,7 +3073,7 @@
       </c>
       <c r="E20" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H20" s="9" t="str">
         <v>mexico</v>
@@ -3105,7 +3107,7 @@
       </c>
       <c r="E21" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H21" s="9" t="str">
         <v>netherlands</v>
@@ -3137,7 +3139,7 @@
       </c>
       <c r="E22" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H22" s="9" t="str">
         <v>norway</v>
@@ -3171,14 +3173,14 @@
       </c>
       <c r="E23" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H23" s="9" t="str">
         <v>peru</v>
       </c>
       <c r="I23" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J23" s="10">
         <v>46223</v>
@@ -3203,7 +3205,7 @@
       </c>
       <c r="E24" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H24" s="9" t="str">
         <v>poland</v>
@@ -3237,7 +3239,7 @@
       </c>
       <c r="E25" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H25" s="9" t="str">
         <v>portugal</v>
@@ -3269,14 +3271,14 @@
       </c>
       <c r="E26" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H26" s="9" t="str">
         <v>romania</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J26" s="10">
         <v>46224</v>
@@ -3303,7 +3305,7 @@
       </c>
       <c r="E27" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H27" s="9" t="str">
         <v>saudi-arabia</v>
@@ -3335,7 +3337,7 @@
       </c>
       <c r="E28" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H28" s="9" t="str">
         <v>scotland</v>
@@ -3369,7 +3371,7 @@
       </c>
       <c r="E29" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H29" s="9" t="str">
         <v>spain</v>
@@ -3401,19 +3403,21 @@
       </c>
       <c r="E30" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H30" s="9" t="str">
         <v>sweden</v>
       </c>
       <c r="I30" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J30" s="10">
-        <v>46252</v>
-      </c>
-      <c r="K30" s="9"/>
+        <v>46229</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
@@ -3433,7 +3437,7 @@
       </c>
       <c r="E31" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H31" s="9" t="str">
         <v>switzerland</v>
@@ -4770,7 +4774,7 @@
       </c>
       <c r="E92" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -4791,7 +4795,7 @@
       </c>
       <c r="E93" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -4812,7 +4816,7 @@
       </c>
       <c r="E94" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -4833,7 +4837,7 @@
       </c>
       <c r="E95" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -4854,7 +4858,7 @@
       </c>
       <c r="E96" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -4875,7 +4879,7 @@
       </c>
       <c r="E97" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -4896,7 +4900,7 @@
       </c>
       <c r="E98" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -4917,7 +4921,7 @@
       </c>
       <c r="E99" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -4938,7 +4942,7 @@
       </c>
       <c r="E100" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -4959,7 +4963,7 @@
       </c>
       <c r="E101" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -4980,7 +4984,7 @@
       </c>
       <c r="E102" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -5001,7 +5005,7 @@
       </c>
       <c r="E103" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -5022,7 +5026,7 @@
       </c>
       <c r="E104" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -5043,7 +5047,7 @@
       </c>
       <c r="E105" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -11424,7 +11428,7 @@
       </c>
       <c r="E410" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.3">
@@ -11445,7 +11449,7 @@
       </c>
       <c r="E411" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.3">
@@ -11466,7 +11470,7 @@
       </c>
       <c r="E412" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.3">
@@ -11487,7 +11491,7 @@
       </c>
       <c r="E413" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.3">
@@ -11508,7 +11512,7 @@
       </c>
       <c r="E414" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.3">
@@ -11529,7 +11533,7 @@
       </c>
       <c r="E415" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.3">
@@ -11550,7 +11554,7 @@
       </c>
       <c r="E416" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.3">
@@ -11571,7 +11575,7 @@
       </c>
       <c r="E417" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.3">
@@ -11592,7 +11596,7 @@
       </c>
       <c r="E418" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.3">
@@ -11613,7 +11617,7 @@
       </c>
       <c r="E419" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.3">
@@ -11634,7 +11638,7 @@
       </c>
       <c r="E420" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.3">
@@ -11655,7 +11659,7 @@
       </c>
       <c r="E421" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.3">
@@ -11676,7 +11680,7 @@
       </c>
       <c r="E422" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.3">
@@ -11697,7 +11701,7 @@
       </c>
       <c r="E423" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.3">
@@ -11718,7 +11722,7 @@
       </c>
       <c r="E424" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.3">
@@ -11739,7 +11743,7 @@
       </c>
       <c r="E425" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.3">
@@ -11760,7 +11764,7 @@
       </c>
       <c r="E426" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.3">
@@ -11781,7 +11785,7 @@
       </c>
       <c r="E427" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.3">
@@ -12558,7 +12562,7 @@
       </c>
       <c r="E464" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
@@ -12579,7 +12583,7 @@
       </c>
       <c r="E465" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
@@ -12600,7 +12604,7 @@
       </c>
       <c r="E466" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
@@ -12621,7 +12625,7 @@
       </c>
       <c r="E467" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
@@ -12642,7 +12646,7 @@
       </c>
       <c r="E468" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
@@ -12663,7 +12667,7 @@
       </c>
       <c r="E469" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
@@ -12684,7 +12688,7 @@
       </c>
       <c r="E470" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
@@ -12705,7 +12709,7 @@
       </c>
       <c r="E471" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
@@ -12726,7 +12730,7 @@
       </c>
       <c r="E472" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
@@ -12747,7 +12751,7 @@
       </c>
       <c r="E473" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.3">
@@ -12768,7 +12772,7 @@
       </c>
       <c r="E474" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.3">
@@ -12789,7 +12793,7 @@
       </c>
       <c r="E475" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.3">
@@ -12810,7 +12814,7 @@
       </c>
       <c r="E476" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.3">
@@ -12831,7 +12835,7 @@
       </c>
       <c r="E477" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
@@ -12852,7 +12856,7 @@
       </c>
       <c r="E478" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.3">
@@ -12873,7 +12877,7 @@
       </c>
       <c r="E479" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
@@ -14384,7 +14388,7 @@
       </c>
       <c r="E552" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.3">
@@ -14405,7 +14409,7 @@
       </c>
       <c r="E553" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.3">
@@ -14426,7 +14430,7 @@
       </c>
       <c r="E554" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.3">
@@ -14447,7 +14451,7 @@
       </c>
       <c r="E555" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.3">
@@ -14468,7 +14472,7 @@
       </c>
       <c r="E556" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.3">
@@ -14489,7 +14493,7 @@
       </c>
       <c r="E557" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.3">
@@ -14510,7 +14514,7 @@
       </c>
       <c r="E558" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.3">
@@ -14531,7 +14535,7 @@
       </c>
       <c r="E559" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.3">
@@ -14552,7 +14556,7 @@
       </c>
       <c r="E560" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.3">
@@ -14573,7 +14577,7 @@
       </c>
       <c r="E561" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.3">
@@ -14594,7 +14598,7 @@
       </c>
       <c r="E562" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.3">
@@ -14615,7 +14619,7 @@
       </c>
       <c r="E563" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.3">
@@ -14636,7 +14640,7 @@
       </c>
       <c r="E564" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.3">
@@ -14657,7 +14661,7 @@
       </c>
       <c r="E565" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.3">
@@ -14678,7 +14682,7 @@
       </c>
       <c r="E566" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.3">
@@ -14699,7 +14703,7 @@
       </c>
       <c r="E567" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.3">

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02E15ED-FC5A-4224-8E5B-CD04BEE41C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF14C381-3CDA-4C4A-80E3-1C2351578325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="626">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -342,9 +342,6 @@
     <t>europe/belgium/club-brugge-kv</t>
   </si>
   <si>
-    <t>europe/belgium/fcv-dender-eh</t>
-  </si>
-  <si>
     <t>europe/belgium/krc-genk</t>
   </si>
   <si>
@@ -369,12 +366,6 @@
     <t>europe/belgium/ru-saint-gilloise</t>
   </si>
   <si>
-    <t>europe/belgium/sv-zulte-waregem</t>
-  </si>
-  <si>
-    <t>europe/belgium/kvc-westerlo</t>
-  </si>
-  <si>
     <t>n-s-america/brazil/clube-atletico-mineiro</t>
   </si>
   <si>
@@ -711,9 +702,6 @@
     <t>uk-ireland/england/ipswich-town-fc</t>
   </si>
   <si>
-    <t>uk-ireland/england/leicester-city-fc</t>
-  </si>
-  <si>
     <t>uk-ireland/england/middlesbrough-fc</t>
   </si>
   <si>
@@ -723,9 +711,6 @@
     <t>uk-ireland/england/norwich-city-fc</t>
   </si>
   <si>
-    <t>uk-ireland/england/oxford-united-fc</t>
-  </si>
-  <si>
     <t>uk-ireland/england/portsmouth-fc</t>
   </si>
   <si>
@@ -738,9 +723,6 @@
     <t>uk-ireland/england/sheffield-united-fc</t>
   </si>
   <si>
-    <t>uk-ireland/england/sheffield-wednesday-fc</t>
-  </si>
-  <si>
     <t>uk-ireland/england/southampton-fc</t>
   </si>
   <si>
@@ -993,18 +975,12 @@
     <t>europe/norway/sk-brann</t>
   </si>
   <si>
-    <t>europe/norway/bryne-fk</t>
-  </si>
-  <si>
     <t>europe/norway/fredrikstad-fk</t>
   </si>
   <si>
     <t>europe/norway/ham-kam</t>
   </si>
   <si>
-    <t>europe/norway/fk-haugesund</t>
-  </si>
-  <si>
     <t>europe/norway/kfum-kameratene-oslo</t>
   </si>
   <si>
@@ -1023,9 +999,6 @@
     <t>europe/norway/sarpsborg-08-ff</t>
   </si>
   <si>
-    <t>europe/norway/stromsgodset</t>
-  </si>
-  <si>
     <t>europe/norway/tromso-il</t>
   </si>
   <si>
@@ -1128,9 +1101,6 @@
     <t>europe/poland/zaglebie-lubin</t>
   </si>
   <si>
-    <t>europe/portugal/avs-futebol-sad</t>
-  </si>
-  <si>
     <t>europe/portugal/fc-alverca</t>
   </si>
   <si>
@@ -1179,9 +1149,6 @@
     <t>europe/portugal/sporting-cp</t>
   </si>
   <si>
-    <t>europe/portugal/cd-tondela</t>
-  </si>
-  <si>
     <t>europe/romania/fc-botosani</t>
   </si>
   <si>
@@ -1320,24 +1287,12 @@
     <t>europe/spain/granada-cf</t>
   </si>
   <si>
-    <t>europe/spain/sd-huesca</t>
-  </si>
-  <si>
-    <t>europe/spain/deportivo-de-la-coruna</t>
-  </si>
-  <si>
     <t>europe/spain/malaga-cf</t>
   </si>
   <si>
-    <t>europe/spain/cd-mirandes</t>
-  </si>
-  <si>
     <t>europe/spain/racing-de-santander</t>
   </si>
   <si>
-    <t>europe/spain/real-zaragoza</t>
-  </si>
-  <si>
     <t>europe/sweden/aik</t>
   </si>
   <si>
@@ -1506,9 +1461,6 @@
     <t>europe/spain/ad-ceuta-fc</t>
   </si>
   <si>
-    <t>europe/spain/cultural-y-deportiva-leonesa</t>
-  </si>
-  <si>
     <t>europe/spain/real-sociedad-b</t>
   </si>
   <si>
@@ -1936,6 +1888,54 @@
   </si>
   <si>
     <t>rest-of-the-world/saudi-arabia/al-faisaly-fc</t>
+  </si>
+  <si>
+    <t>europe/belgium/sk-beveren</t>
+  </si>
+  <si>
+    <t>europe/belgium/kv-kortrijk</t>
+  </si>
+  <si>
+    <t>europe/belgium/lommel-sk</t>
+  </si>
+  <si>
+    <t>uk-ireland/england/bolton-wanderers-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/england/cardiff-city-fc</t>
+  </si>
+  <si>
+    <t>uk-ireland/england/lincoln-city-fc</t>
+  </si>
+  <si>
+    <t>europe/norway/aalesunds-fk</t>
+  </si>
+  <si>
+    <t>europe/norway/lillestrom-sk</t>
+  </si>
+  <si>
+    <t>europe/norway/ik-start</t>
+  </si>
+  <si>
+    <t>europe/portugal/academico-de-viseu-fc</t>
+  </si>
+  <si>
+    <t>europe/portugal/maritimo</t>
+  </si>
+  <si>
+    <t>europe/spain/deportivo-de-a-coruna</t>
+  </si>
+  <si>
+    <t>europe/spain/celta-de-vigo-b</t>
+  </si>
+  <si>
+    <t>europe/spain/cd-eldense</t>
+  </si>
+  <si>
+    <t>europe/spain/ce-sabadell-fc</t>
+  </si>
+  <si>
+    <t>europe/spain/cd-tenerife</t>
   </si>
 </sst>
 </file>
@@ -2443,10 +2443,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -2455,7 +2455,7 @@
         <v>club-atletico-aldosivi</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2481,7 +2481,7 @@
         <v>46227</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2490,7 +2490,7 @@
         <v>argentinos-juniors</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C3" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2522,7 +2522,7 @@
         <v>club-atletico-tucuman</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2547,7 +2547,7 @@
         <v>46237</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2556,7 +2556,7 @@
         <v>club-atletico-banfield</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C5" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2580,7 +2580,9 @@
       <c r="J5" s="10">
         <v>46241</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="9" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
@@ -2588,7 +2590,7 @@
         <v>club-atletico-barracas-central</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C6" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2613,7 +2615,7 @@
         <v>46050</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2622,7 +2624,7 @@
         <v>club-atletico-belgrano</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C7" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2647,7 +2649,7 @@
         <v>46224</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2656,7 +2658,7 @@
         <v>club-atletico-boca-juniors</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C8" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2681,7 +2683,7 @@
         <v>46052</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2690,7 +2692,7 @@
         <v>club-atletico-central-cordoba</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C9" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2715,7 +2717,7 @@
         <v>46230</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2724,7 +2726,7 @@
         <v>defensa-y-justicia</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C10" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2749,7 +2751,7 @@
         <v>46235</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -2758,7 +2760,7 @@
         <v>deportivo-riestra</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C11" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2783,7 +2785,7 @@
         <v>46231</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2792,7 +2794,7 @@
         <v>club-estudiantes-de-la-plata</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C12" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2817,7 +2819,7 @@
         <v>46230</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2826,7 +2828,7 @@
         <v>estudiantes-de-rio-cuarto</v>
       </c>
       <c r="B13" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2851,7 +2853,7 @@
         <v>46220</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2860,7 +2862,7 @@
         <v>club-de-gimnasia-la-plata</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2879,12 +2881,14 @@
       </c>
       <c r="I14" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J14" s="10">
         <v>46252</v>
       </c>
-      <c r="K14" s="9"/>
+      <c r="K14" s="9" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
@@ -2892,7 +2896,7 @@
         <v>club-gimnasia-de-mendoza</v>
       </c>
       <c r="B15" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2917,7 +2921,7 @@
         <v>46116</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2926,7 +2930,7 @@
         <v>club-atletico-huracan</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C16" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2958,7 +2962,7 @@
         <v>club-sportivo-independiente-rivadavia</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C17" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2990,7 +2994,7 @@
         <v>club-atletico-independiente</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C18" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3022,7 +3026,7 @@
         <v>instituto-atletico-central-cordoba</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C19" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3054,7 +3058,7 @@
         <v>club-atletico-lanus</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C20" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3079,7 +3083,7 @@
         <v>46220</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -3088,7 +3092,7 @@
         <v>club-atletico-newells-old-boys</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C21" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3112,7 +3116,9 @@
       <c r="J21" s="10">
         <v>46244</v>
       </c>
-      <c r="K21" s="9"/>
+      <c r="K21" s="9" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
@@ -3120,7 +3126,7 @@
         <v>club-atletico-platense</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C22" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3145,7 +3151,7 @@
         <v>46095</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -3154,7 +3160,7 @@
         <v>racing-club-de-avellaneda</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C23" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3179,7 +3185,7 @@
         <v>46223</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -3188,7 +3194,7 @@
         <v>club-atletico-river-plate</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C24" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3213,7 +3219,7 @@
         <v>46231</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -3222,7 +3228,7 @@
         <v>club-atletico-rosario-central</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C25" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3246,7 +3252,9 @@
       <c r="J25" s="10">
         <v>46243</v>
       </c>
-      <c r="K25" s="9"/>
+      <c r="K25" s="9" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
@@ -3254,7 +3262,7 @@
         <v>san-lorenzo-de-almagro</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C26" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3279,7 +3287,7 @@
         <v>46224</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -3288,7 +3296,7 @@
         <v>club-atletico-sarmiento-junin</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C27" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3313,7 +3321,7 @@
         <v>46242</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -3322,7 +3330,7 @@
         <v>club-atletico-talleres</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C28" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3347,7 +3355,7 @@
         <v>46238</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -3356,7 +3364,7 @@
         <v>club-atletico-tigre</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C29" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3375,12 +3383,14 @@
       </c>
       <c r="I29" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J29" s="10">
         <v>46252</v>
       </c>
-      <c r="K29" s="9"/>
+      <c r="K29" s="9" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
@@ -3388,7 +3398,7 @@
         <v>club-atletico-union-de-santa-fe</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C30" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3413,7 +3423,7 @@
         <v>46229</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -3422,7 +3432,7 @@
         <v>club-atletico-velez-sarsfield</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C31" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3447,7 +3457,7 @@
         <v>46230</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -3456,7 +3466,7 @@
         <v>adelaide-united-fc</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3481,7 +3491,7 @@
         <v>46074</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -3490,7 +3500,7 @@
         <v>auckland-fc</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3515,7 +3525,7 @@
         <v>46121</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -3524,7 +3534,7 @@
         <v>brisbane-roar-fc</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="C34" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3549,7 +3559,7 @@
         <v>46121</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -3558,7 +3568,7 @@
         <v>central-coast-mariners-fc</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3583,7 +3593,7 @@
         <v>macarthur-fc</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3604,7 +3614,7 @@
         <v>melbourne-city-fc</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3625,7 +3635,7 @@
         <v>melbourne-victory-fc</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3646,7 +3656,7 @@
         <v>newcastle-jets-fc</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3667,7 +3677,7 @@
         <v>perth-glory-fc</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C40" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3688,7 +3698,7 @@
         <v>sydney-fc</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3709,7 +3719,7 @@
         <v>wellington-phoenix-fc</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3730,7 +3740,7 @@
         <v>western-sydney-wanderers-fc</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3751,7 +3761,7 @@
         <v>sc-austria-lustenau</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="C44" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4042,10 +4052,10 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cercle-brugge-ksv</v>
+        <v>sk-beveren</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>91</v>
+        <v>610</v>
       </c>
       <c r="C58" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4063,10 +4073,10 @@
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>royal-charleroi-sc</v>
+        <v>cercle-brugge-ksv</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C59" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4084,10 +4094,10 @@
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-brugge-kv</v>
+        <v>royal-charleroi-sc</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C60" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4105,10 +4115,10 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fcv-dender-eh</v>
+        <v>club-brugge-kv</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C61" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4129,7 +4139,7 @@
         <v>krc-genk</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C62" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4150,7 +4160,7 @@
         <v>kaa-gent</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C63" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4168,10 +4178,10 @@
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kv-mechelen</v>
+        <v>kv-kortrijk</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>97</v>
+        <v>611</v>
       </c>
       <c r="C64" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4189,10 +4199,10 @@
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>oh-leuven</v>
+        <v>kv-mechelen</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C65" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4210,10 +4220,10 @@
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>raal-la-louviere</v>
+        <v>oh-leuven</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C66" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4231,10 +4241,10 @@
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>standard-liege</v>
+        <v>lommel-sk</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>100</v>
+        <v>612</v>
       </c>
       <c r="C67" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4252,10 +4262,10 @@
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sint-truidense-vv</v>
+        <v>raal-la-louviere</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C68" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4273,10 +4283,10 @@
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ru-saint-gilloise</v>
+        <v>standard-liege</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C69" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4294,10 +4304,10 @@
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sv-zulte-waregem</v>
+        <v>sint-truidense-vv</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C70" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4315,10 +4325,10 @@
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kvc-westerlo</v>
+        <v>ru-saint-gilloise</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C71" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4339,7 +4349,7 @@
         <v>club-athletico-paranaense</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="C72" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4360,7 +4370,7 @@
         <v>clube-atletico-mineiro</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C73" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4381,7 +4391,7 @@
         <v>esporte-clube-bahia</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C74" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4402,7 +4412,7 @@
         <v>botafogo-de-futebol-e-regatas</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C75" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4423,7 +4433,7 @@
         <v>red-bull-bragantino</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C76" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4444,7 +4454,7 @@
         <v>associacao-chapecoense-de-futebol</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="C77" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4465,7 +4475,7 @@
         <v>sport-club-corinthians-paulista</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C78" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4486,7 +4496,7 @@
         <v>coritiba-football-club</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C79" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4507,7 +4517,7 @@
         <v>cruzeiro-esporte-clube</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C80" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4528,7 +4538,7 @@
         <v>clube-de-regatas-do-flamengo</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C81" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4549,7 +4559,7 @@
         <v>fluminense-fc</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C82" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4570,7 +4580,7 @@
         <v>gremio-football-porto-alagrense</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C83" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4591,7 +4601,7 @@
         <v>sport-club-internacional</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C84" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4612,7 +4622,7 @@
         <v>mirassol-fc</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C85" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4633,7 +4643,7 @@
         <v>sociedade-esportiva-palmeiras</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C86" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4654,7 +4664,7 @@
         <v>clube-do-remo</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C87" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4675,7 +4685,7 @@
         <v>santos-fc</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C88" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4696,7 +4706,7 @@
         <v>sao-paulo-fc</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C89" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4717,7 +4727,7 @@
         <v>cr-vasco-da-gama</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C90" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4738,7 +4748,7 @@
         <v>esporte-clube-vitoria</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4759,7 +4769,7 @@
         <v>arda-kardzhali</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4780,7 +4790,7 @@
         <v>botev-plovdiv</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C93" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4801,7 +4811,7 @@
         <v>botev-vratsa</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C94" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4822,7 +4832,7 @@
         <v>cherno-more</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C95" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4843,7 +4853,7 @@
         <v>fc-cska-1948-sofia</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C96" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4864,7 +4874,7 @@
         <v>cska-sofia</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C97" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4885,7 +4895,7 @@
         <v>fc-dunav-ruse</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="C98" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4906,7 +4916,7 @@
         <v>levski-sofia</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C99" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4927,7 +4937,7 @@
         <v>lokomotiv-plovdiv</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C100" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4948,7 +4958,7 @@
         <v>fc-lokomotiv-1929-sofia</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C101" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4969,7 +4979,7 @@
         <v>ludogorets</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C102" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4990,7 +5000,7 @@
         <v>pfc-septemvri-sofia</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C103" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5011,7 +5021,7 @@
         <v>slavia-sofia</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C104" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5032,7 +5042,7 @@
         <v>fc-spartak-varna</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C105" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5053,7 +5063,7 @@
         <v>audax-italiano</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C106" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5074,7 +5084,7 @@
         <v>cd-cobresal</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C107" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5095,7 +5105,7 @@
         <v>colo-colo</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C108" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5116,7 +5126,7 @@
         <v>coquimbo-unido</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C109" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5137,7 +5147,7 @@
         <v>deportes-concepcion</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="C110" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5158,7 +5168,7 @@
         <v>everton-de-vina-del-mar</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C111" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5179,7 +5189,7 @@
         <v>cd-huachipato</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C112" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5200,7 +5210,7 @@
         <v>deportes-la-serena</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C113" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5221,7 +5231,7 @@
         <v>deportes-limache</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C114" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5242,7 +5252,7 @@
         <v>deportivo-nublense</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C115" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5263,7 +5273,7 @@
         <v>o-higgins-fc</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C116" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5284,7 +5294,7 @@
         <v>cd-palestino</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C117" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5305,7 +5315,7 @@
         <v>union-la-calera</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C118" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5326,7 +5336,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C119" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5347,7 +5357,7 @@
         <v>club-universidad-de-chile</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C120" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5368,7 +5378,7 @@
         <v>cd-universidad-de-concepcion</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C121" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5515,7 +5525,7 @@
         <v>cucuta-deportivo-fc</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C128" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5599,7 +5609,7 @@
         <v>internacional-de-bogota</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C132" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5620,7 +5630,7 @@
         <v>jaguares-de-cordoba</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="C133" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5809,7 +5819,7 @@
         <v>dinamo-zagreb</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C142" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5830,7 +5840,7 @@
         <v>gorica</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C143" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5851,7 +5861,7 @@
         <v>hajduk-split</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C144" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5872,7 +5882,7 @@
         <v>istra-1961</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C145" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5893,7 +5903,7 @@
         <v>lokomotiva-zagreb</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C146" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5914,7 +5924,7 @@
         <v>osijek</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C147" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5935,7 +5945,7 @@
         <v>rijeka</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C148" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5956,7 +5966,7 @@
         <v>nk-rudes</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="C149" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5977,7 +5987,7 @@
         <v>slaven-belupo</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C150" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5998,7 +6008,7 @@
         <v>varazdin</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C151" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6019,7 +6029,7 @@
         <v>sk-artis-brno</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="C152" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6040,7 +6050,7 @@
         <v>bohemians-1905</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C153" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6061,7 +6071,7 @@
         <v>fc-zbrojovka-brno</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="C154" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6082,7 +6092,7 @@
         <v>fc-hradec-kralove</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C155" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6103,7 +6113,7 @@
         <v>fk-jablonec</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C156" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6124,7 +6134,7 @@
         <v>fc-slovan-liberec</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C157" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6145,7 +6155,7 @@
         <v>fk-mlada-boleslav</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C158" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6166,7 +6176,7 @@
         <v>fc-banik-ostrava</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C159" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6187,7 +6197,7 @@
         <v>fk-pardubice</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C160" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6208,7 +6218,7 @@
         <v>fc-viktoria-plzen</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C161" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6229,7 +6239,7 @@
         <v>sk-sigma-olomouc</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C162" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6250,7 +6260,7 @@
         <v>slavia-prague</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C163" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6271,7 +6281,7 @@
         <v>fc-slovacko</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C164" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6292,7 +6302,7 @@
         <v>sparta-prague</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C165" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6313,7 +6323,7 @@
         <v>fk-teplice</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C166" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6334,7 +6344,7 @@
         <v>fc-fastav-zlin</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C167" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6355,7 +6365,7 @@
         <v>aarhus</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C168" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6376,7 +6386,7 @@
         <v>brondby</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C169" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6397,7 +6407,7 @@
         <v>fc-copenhagen</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C170" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6418,7 +6428,7 @@
         <v>ac-horsens</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="C171" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6439,7 +6449,7 @@
         <v>lyngby-bk</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="C172" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6460,7 +6470,7 @@
         <v>fc-midtjylland</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C173" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6481,7 +6491,7 @@
         <v>fc-nordsjaelland</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C174" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6502,7 +6512,7 @@
         <v>odense-boldklub</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C175" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6523,7 +6533,7 @@
         <v>randers-fc</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C176" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6544,7 +6554,7 @@
         <v>silkeborg-if</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C177" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6565,7 +6575,7 @@
         <v>sonderjyske</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C178" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6586,7 +6596,7 @@
         <v>viborg-ff</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C179" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6607,7 +6617,7 @@
         <v>sd-aucas</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C180" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6628,7 +6638,7 @@
         <v>barcelona-sc</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="C181" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6649,7 +6659,7 @@
         <v>delfin-sc</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C182" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6670,7 +6680,7 @@
         <v>cd-cuenca</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C183" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6691,7 +6701,7 @@
         <v>cs-emelec</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="C184" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6712,7 +6722,7 @@
         <v>guayaquil-city-fc</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6733,7 +6743,7 @@
         <v>csd-independiente-del-valle</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6754,7 +6764,7 @@
         <v>ldu-quito</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C187" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6775,7 +6785,7 @@
         <v>leones-fc</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="C188" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6796,7 +6806,7 @@
         <v>libertad-fc</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="C189" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6817,7 +6827,7 @@
         <v>csd-macara</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C190" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6838,7 +6848,7 @@
         <v>manta-fc</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="C191" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6859,7 +6869,7 @@
         <v>mushuc-runa-sc</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="C192" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6880,7 +6890,7 @@
         <v>orense-sc</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="C193" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6901,7 +6911,7 @@
         <v>tecnico-universitario</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="C194" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6922,7 +6932,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="C195" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6955,7 +6965,7 @@
       </c>
       <c r="E196" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
@@ -6976,7 +6986,7 @@
       </c>
       <c r="E197" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
@@ -6997,7 +7007,7 @@
       </c>
       <c r="E198" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
@@ -7018,7 +7028,7 @@
       </c>
       <c r="E199" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
@@ -7039,16 +7049,16 @@
       </c>
       <c r="E200" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>burnley-fc</v>
+        <v>chelsea-fc</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C201" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7060,16 +7070,16 @@
       </c>
       <c r="E201" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chelsea-fc</v>
+        <v>coventry-city-fc</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="C202" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7081,7 +7091,7 @@
       </c>
       <c r="E202" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
@@ -7102,7 +7112,7 @@
       </c>
       <c r="E203" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -7123,7 +7133,7 @@
       </c>
       <c r="E204" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -7144,16 +7154,16 @@
       </c>
       <c r="E205" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>leeds-united-fc</v>
+        <v>hull-city-fc</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="C206" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7165,16 +7175,16 @@
       </c>
       <c r="E206" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>liverpool-fc</v>
+        <v>ipswich-town-fc</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="C207" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7186,16 +7196,16 @@
       </c>
       <c r="E207" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>manchester-city-fc</v>
+        <v>leeds-united-fc</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C208" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7207,16 +7217,16 @@
       </c>
       <c r="E208" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>manchester-united-fc</v>
+        <v>liverpool-fc</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C209" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7228,16 +7238,16 @@
       </c>
       <c r="E209" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>newcastle-united-fc</v>
+        <v>manchester-city-fc</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C210" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7249,16 +7259,16 @@
       </c>
       <c r="E210" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nottingham-forest-fc</v>
+        <v>manchester-united-fc</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C211" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7270,16 +7280,16 @@
       </c>
       <c r="E211" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sunderland-afc</v>
+        <v>newcastle-united-fc</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C212" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7291,16 +7301,16 @@
       </c>
       <c r="E212" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tottenham-hotspur-fc</v>
+        <v>nottingham-forest-fc</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C213" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7312,16 +7322,16 @@
       </c>
       <c r="E213" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>west-ham-united-fc</v>
+        <v>sunderland-afc</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C214" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7333,16 +7343,16 @@
       </c>
       <c r="E214" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wolverhampton-wanderers-fc</v>
+        <v>tottenham-hotspur-fc</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C215" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7354,7 +7364,7 @@
       </c>
       <c r="E215" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
@@ -7363,18 +7373,18 @@
         <v>birmingham-city-fc</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C216" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D216" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E216" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
@@ -7383,158 +7393,158 @@
         <v>blackburn-rovers-fc</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C217" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D217" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E217" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bristol-city-fc</v>
+        <v>bolton-wanderers-fc</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>211</v>
+        <v>613</v>
       </c>
       <c r="C218" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D218" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E218" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>charlton-athletic-fc</v>
+        <v>bristol-city-fc</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C219" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D219" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E219" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>coventry-city-fc</v>
+        <v>burnley-fc</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>213</v>
+        <v>25</v>
       </c>
       <c r="C220" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D220" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E220" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>derby-county-fc</v>
+        <v>cardiff-city-fc</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>214</v>
+        <v>614</v>
       </c>
       <c r="C221" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D221" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E221" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hull-city-fc</v>
+        <v>charlton-athletic-fc</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C222" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D222" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E222" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ipswich-town-fc</v>
+        <v>derby-county-fc</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C223" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D223" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E223" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>leicester-city-fc</v>
+        <v>lincoln-city-fc</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>217</v>
+        <v>615</v>
       </c>
       <c r="C224" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D224" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E224" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
@@ -7543,18 +7553,18 @@
         <v>middlesbrough-fc</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C225" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D225" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E225" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
@@ -7563,18 +7573,18 @@
         <v>millwall-fc</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C226" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D226" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E226" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
@@ -7583,238 +7593,238 @@
         <v>norwich-city-fc</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C227" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D227" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E227" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>oxford-united-fc</v>
+        <v>portsmouth-fc</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C228" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D228" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E228" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>portsmouth-fc</v>
+        <v>preston-north-end-fc</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C229" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D229" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E229" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>preston-north-end-fc</v>
+        <v>queens-park-rangers-fc</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C230" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D230" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E230" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>queens-park-rangers-fc</v>
+        <v>sheffield-united-fc</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C231" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D231" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E231" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sheffield-united-fc</v>
+        <v>southampton-fc</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C232" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D232" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E232" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sheffield-wednesday-fc</v>
+        <v>stoke-city-fc</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C233" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D233" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E233" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>southampton-fc</v>
+        <v>swansea-city-afc</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C234" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D234" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E234" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>stoke-city-fc</v>
+        <v>watford-fc</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C235" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D235" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E235" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>swansea-city-afc</v>
+        <v>west-bromwich-albion-fc</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C236" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D236" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E236" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>watford-fc</v>
+        <v>west-ham-united-fc</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>230</v>
+        <v>38</v>
       </c>
       <c r="C237" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D237" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E237" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>west-bromwich-albion-fc</v>
+        <v>wolverhampton-wanderers-fc</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>231</v>
+        <v>39</v>
       </c>
       <c r="C238" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D238" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E238" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
@@ -7823,18 +7833,18 @@
         <v>wrexham-afc</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C239" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D239" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="E239" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
@@ -7843,7 +7853,7 @@
         <v>if-gnistan</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C240" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7864,7 +7874,7 @@
         <v>hjk-helsinki</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="C241" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7885,7 +7895,7 @@
         <v>fc-ilves</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7906,7 +7916,7 @@
         <v>fc-inter-turku</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7927,7 +7937,7 @@
         <v>ff-jaro</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7948,7 +7958,7 @@
         <v>kuopion-palloseura</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="C245" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7969,7 +7979,7 @@
         <v>fc-lahti</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="C246" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7990,7 +8000,7 @@
         <v>ifk-mariehamn</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="C247" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8011,7 +8021,7 @@
         <v>ac-oulu</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="C248" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8032,7 +8042,7 @@
         <v>sjk</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8053,7 +8063,7 @@
         <v>tps-turku</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8074,7 +8084,7 @@
         <v>vaasan-palloseura</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8095,7 +8105,7 @@
         <v>angers-sco</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C252" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8116,7 +8126,7 @@
         <v>aj-auxerre</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C253" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8137,7 +8147,7 @@
         <v>stade-brestois-29</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C254" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8158,7 +8168,7 @@
         <v>le-havre-ac</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C255" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8179,7 +8189,7 @@
         <v>rc-lens</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C256" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8200,7 +8210,7 @@
         <v>lille-osc</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C257" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8221,7 +8231,7 @@
         <v>fc-lorient</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="C258" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8242,7 +8252,7 @@
         <v>olympique-lyonnais</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C259" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8263,7 +8273,7 @@
         <v>olympique-de-marseille</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C260" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8284,7 +8294,7 @@
         <v>fc-metz</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="C261" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8305,7 +8315,7 @@
         <v>as-monaco-fc</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C262" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8326,7 +8336,7 @@
         <v>fc-nantes</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C263" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8347,7 +8357,7 @@
         <v>ogc-nice</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C264" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8368,7 +8378,7 @@
         <v>paris-fc</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C265" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8389,7 +8399,7 @@
         <v>paris-saint-germain-fc</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C266" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8410,7 +8420,7 @@
         <v>stade-rennais-fc</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C267" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8431,7 +8441,7 @@
         <v>rc-strasbourg-alsace</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C268" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8452,7 +8462,7 @@
         <v>toulouse-fc</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C269" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8557,7 +8567,7 @@
         <v>fc-koln</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="C274" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8620,7 +8630,7 @@
         <v>hamburger-sv</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="C277" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8851,7 +8861,7 @@
         <v>arminia-bielefeld</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C288" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8893,7 +8903,7 @@
         <v>eintracht-braunschweig</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C290" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8914,7 +8924,7 @@
         <v>fc-energie-cottbus</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="C291" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8935,7 +8945,7 @@
         <v>darmstadt-98</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C292" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8956,7 +8966,7 @@
         <v>dynamo-dresden</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C293" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8977,7 +8987,7 @@
         <v>greuther-furth</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C294" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8998,7 +9008,7 @@
         <v>hannover-96</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C295" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9040,7 +9050,7 @@
         <v>hertha-berlin</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C297" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9061,7 +9071,7 @@
         <v>fc-kaiserslautern</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C298" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9082,7 +9092,7 @@
         <v>karlsruher-sc</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C299" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9124,7 +9134,7 @@
         <v>fc-magdeburg</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C301" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9145,7 +9155,7 @@
         <v>fc-nurnberg</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C302" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9166,7 +9176,7 @@
         <v>vfl-osnabruck</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="C303" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9229,7 +9239,7 @@
         <v>aek-athens-fc</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C306" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9250,7 +9260,7 @@
         <v>ael-fc</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C307" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9271,7 +9281,7 @@
         <v>aris-thessaloniki-fc</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="C308" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9292,7 +9302,7 @@
         <v>asteras-tripolis-fc</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="C309" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9313,7 +9323,7 @@
         <v>atromitos-fc</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="C310" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9334,7 +9344,7 @@
         <v>ae-kifisia-fc</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="C311" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9355,7 +9365,7 @@
         <v>levadiakos-fc</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="C312" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9376,7 +9386,7 @@
         <v>ofi-crete-fc</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="C313" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9397,7 +9407,7 @@
         <v>olympiacos-fc</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C314" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9418,7 +9428,7 @@
         <v>panathinaikos-fc</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="C315" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9439,7 +9449,7 @@
         <v>panetolikos-fc</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C316" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9460,7 +9470,7 @@
         <v>panserraikos-fc</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="C317" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9481,7 +9491,7 @@
         <v>paok-fc</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="C318" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9502,7 +9512,7 @@
         <v>volos-fc</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="C319" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9523,7 +9533,7 @@
         <v>ac-milan</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C320" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9544,7 +9554,7 @@
         <v>as-roma</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C321" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9565,7 +9575,7 @@
         <v>atalanta-bc</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C322" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9586,7 +9596,7 @@
         <v>bologna-fc-1909</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C323" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9607,7 +9617,7 @@
         <v>cagliari-calcio</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C324" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9628,7 +9638,7 @@
         <v>como-1907</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C325" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9649,7 +9659,7 @@
         <v>us-cremonese</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="C326" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9670,7 +9680,7 @@
         <v>acf-fiorentina</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C327" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9691,7 +9701,7 @@
         <v>genoa-cfc</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C328" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9712,7 +9722,7 @@
         <v>inter-milan</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9733,7 +9743,7 @@
         <v>juventus-fc</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C330" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9754,7 +9764,7 @@
         <v>ss-lazio</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C331" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9775,7 +9785,7 @@
         <v>us-lecce</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C332" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9796,7 +9806,7 @@
         <v>ssc-napoli</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C333" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9817,7 +9827,7 @@
         <v>parma-calcio-1913</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C334" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9838,7 +9848,7 @@
         <v>ac-pisa-1909</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C335" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9859,7 +9869,7 @@
         <v>us-sassuolo-calcio</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C336" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9880,7 +9890,7 @@
         <v>torino-fc</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C337" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9901,7 +9911,7 @@
         <v>udinese-calcio</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C338" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9922,7 +9932,7 @@
         <v>hellas-verona-fc</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C339" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9943,7 +9953,7 @@
         <v>atletico-san-luis</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C340" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9964,7 +9974,7 @@
         <v>atlas-fc</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C341" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9985,7 +9995,7 @@
         <v>club-america</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C342" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10006,7 +10016,7 @@
         <v>cruz-azul</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C343" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10027,7 +10037,7 @@
         <v>cd-guadalajara</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C344" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10048,7 +10058,7 @@
         <v>fc-juarez</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C345" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10069,7 +10079,7 @@
         <v>club-leon</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C346" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10090,7 +10100,7 @@
         <v>mazatlan-fc</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C347" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10111,7 +10121,7 @@
         <v>cf-monterrey</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C348" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10132,7 +10142,7 @@
         <v>club-necaxa</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C349" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10153,7 +10163,7 @@
         <v>cf-pachuca</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C350" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10174,7 +10184,7 @@
         <v>club-puebla</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C351" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10195,7 +10205,7 @@
         <v>queretaro-fc</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C352" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10216,7 +10226,7 @@
         <v>santos-laguna</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C353" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10237,7 +10247,7 @@
         <v>tigres-uanl</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C354" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10258,7 +10268,7 @@
         <v>club-tijuana</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C355" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10279,7 +10289,7 @@
         <v>deportivo-toluca-fc</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C356" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10300,7 +10310,7 @@
         <v>unam</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C357" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10321,7 +10331,7 @@
         <v>afc-ajax</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C358" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10342,7 +10352,7 @@
         <v>az-alkmaar</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C359" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10363,7 +10373,7 @@
         <v>sc-cambuur</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="C360" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10384,7 +10394,7 @@
         <v>ado-den-haag</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="C361" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10405,7 +10415,7 @@
         <v>sbv-excelsior</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C362" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10426,7 +10436,7 @@
         <v>feyenoord-rotterdam</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C363" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10447,7 +10457,7 @@
         <v>go-ahead-eagles</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C364" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10468,7 +10478,7 @@
         <v>fc-groningen</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C365" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10489,7 +10499,7 @@
         <v>sc-heerenveen</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C366" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10510,7 +10520,7 @@
         <v>nec-nijmegen</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C367" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10531,7 +10541,7 @@
         <v>psv-eindhoven</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C368" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10552,7 +10562,7 @@
         <v>fortuna-sittard</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C369" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10573,7 +10583,7 @@
         <v>sparta-rotterdam</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C370" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10594,7 +10604,7 @@
         <v>sc-telstar</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C371" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10615,7 +10625,7 @@
         <v>fc-twente</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C372" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10636,7 +10646,7 @@
         <v>fc-utrecht</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C373" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10657,7 +10667,7 @@
         <v>willem-ii</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="C374" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10678,7 +10688,7 @@
         <v>pec-zwolle</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C375" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10696,10 +10706,10 @@
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-bodo-glimt</v>
+        <v>aalesunds-fk</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>309</v>
+        <v>616</v>
       </c>
       <c r="C376" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10717,10 +10727,10 @@
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sk-brann</v>
+        <v>fk-bodo-glimt</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C377" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10738,10 +10748,10 @@
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bryne-fk</v>
+        <v>sk-brann</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C378" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10762,7 +10772,7 @@
         <v>fredrikstad-fk</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C379" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10783,7 +10793,7 @@
         <v>ham-kam</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C380" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10801,10 +10811,10 @@
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-haugesund</v>
+        <v>kfum-kameratene-oslo</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C381" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10822,10 +10832,10 @@
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kfum-kameratene-oslo</v>
+        <v>kristiansund-bk</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C382" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10843,10 +10853,10 @@
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kristiansund-bk</v>
+        <v>lillestrom-sk</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>316</v>
+        <v>617</v>
       </c>
       <c r="C383" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10867,7 +10877,7 @@
         <v>molde-fk</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C384" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10888,7 +10898,7 @@
         <v>rosenborg-bk</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C385" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10909,7 +10919,7 @@
         <v>sandefjord-fotball</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C386" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10930,7 +10940,7 @@
         <v>sarpsborg-08-ff</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C387" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10948,10 +10958,10 @@
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>stromsgodset</v>
+        <v>ik-start</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>321</v>
+        <v>618</v>
       </c>
       <c r="C388" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10972,7 +10982,7 @@
         <v>tromso-il</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C389" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10993,7 +11003,7 @@
         <v>valerenga-fotball</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C390" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11014,7 +11024,7 @@
         <v>viking-fk</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C391" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11035,7 +11045,7 @@
         <v>alianza-lima</v>
       </c>
       <c r="B392" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C392" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11056,7 +11066,7 @@
         <v>asociacion-deportiva-tarma</v>
       </c>
       <c r="B393" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C393" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11077,7 +11087,7 @@
         <v>alianza-atletico</v>
       </c>
       <c r="B394" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C394" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11098,7 +11108,7 @@
         <v>universidad-tecnica-de-cajamarca</v>
       </c>
       <c r="B395" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C395" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11119,7 +11129,7 @@
         <v>club-sportivo-cienciano</v>
       </c>
       <c r="B396" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C396" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11140,7 +11150,7 @@
         <v>comerciantes-unidos</v>
       </c>
       <c r="B397" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C397" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11161,7 +11171,7 @@
         <v>cusco-fc</v>
       </c>
       <c r="B398" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C398" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11182,7 +11192,7 @@
         <v>deportivo-garcilaso</v>
       </c>
       <c r="B399" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C399" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11203,7 +11213,7 @@
         <v>fc-cajamarca</v>
       </c>
       <c r="B400" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="C400" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11224,7 +11234,7 @@
         <v>atletico-grau</v>
       </c>
       <c r="B401" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C401" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11245,7 +11255,7 @@
         <v>sport-huancayo</v>
       </c>
       <c r="B402" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C402" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11266,7 +11276,7 @@
         <v>adc-juan-pablo-ii-college</v>
       </c>
       <c r="B403" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C403" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11287,7 +11297,7 @@
         <v>los-chankas-cyc</v>
       </c>
       <c r="B404" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C404" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11308,7 +11318,7 @@
         <v>fbc-melgar</v>
       </c>
       <c r="B405" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C405" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11329,7 +11339,7 @@
         <v>club-deportivo-moquegua</v>
       </c>
       <c r="B406" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C406" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11350,7 +11360,7 @@
         <v>sport-boys</v>
       </c>
       <c r="B407" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C407" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11371,7 +11381,7 @@
         <v>sporting-cristal</v>
       </c>
       <c r="B408" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C408" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11392,7 +11402,7 @@
         <v>club-universitario-de-deportes</v>
       </c>
       <c r="B409" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C409" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11413,7 +11423,7 @@
         <v>cracovia</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C410" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11434,7 +11444,7 @@
         <v>gornik-zabrze</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C411" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11455,7 +11465,7 @@
         <v>jagiellona-bialystok</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C412" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11476,7 +11486,7 @@
         <v>gks-katowice</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C413" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11497,7 +11507,7 @@
         <v>korona-kielce</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C414" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11518,7 +11528,7 @@
         <v>lech-poznan</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C415" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11539,7 +11549,7 @@
         <v>legia-warsaw</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C416" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11560,7 +11570,7 @@
         <v>motor-lublin</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C417" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11581,7 +11591,7 @@
         <v>piast-gliwice</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C418" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11602,7 +11612,7 @@
         <v>mks-pogon-szczecin</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C419" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11623,7 +11633,7 @@
         <v>radomiak-radom</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C420" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11644,7 +11654,7 @@
         <v>rakow-czestochowa</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C421" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11665,7 +11675,7 @@
         <v>slask-wroclaw</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="C422" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11686,7 +11696,7 @@
         <v>rts-widzew-lodz</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C423" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11707,7 +11717,7 @@
         <v>ks-wieczysta-krokow</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="C424" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11728,7 +11738,7 @@
         <v>wisla-krakow</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="C425" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11749,7 +11759,7 @@
         <v>wisla-plock</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C426" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11770,7 +11780,7 @@
         <v>zaglebie-lubin</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C427" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11788,10 +11798,10 @@
     <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>avs-futebol-sad</v>
+        <v>academico-de-viseu-fc</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>356</v>
+        <v>619</v>
       </c>
       <c r="C428" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11812,7 +11822,7 @@
         <v>fc-alverca</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C429" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11833,7 +11843,7 @@
         <v>fc-arouca</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C430" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11854,7 +11864,7 @@
         <v>benfica</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C431" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11875,7 +11885,7 @@
         <v>braga</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C432" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11896,7 +11906,7 @@
         <v>casa-pia-ac</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C433" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11917,7 +11927,7 @@
         <v>gd-estoril-praia</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C434" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11938,7 +11948,7 @@
         <v>cf-estrela-da-amadora</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C435" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11959,7 +11969,7 @@
         <v>famalicao</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C436" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11980,7 +11990,7 @@
         <v>fc-porto</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C437" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12001,7 +12011,7 @@
         <v>gil-vicente</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C438" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12022,7 +12032,7 @@
         <v>vitoria-de-guimaraes</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C439" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12040,10 +12050,10 @@
     <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>moreirense-fc</v>
+        <v>maritimo</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>368</v>
+        <v>620</v>
       </c>
       <c r="C440" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12061,10 +12071,10 @@
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-nacional</v>
+        <v>moreirense-fc</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C441" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12082,10 +12092,10 @@
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rio-ave-fc</v>
+        <v>cd-nacional</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C442" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12103,10 +12113,10 @@
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>santa-clara</v>
+        <v>rio-ave-fc</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C443" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12124,10 +12134,10 @@
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-cp</v>
+        <v>santa-clara</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C444" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12145,10 +12155,10 @@
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-tondela</v>
+        <v>sporting-cp</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C445" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12169,7 +12179,7 @@
         <v>fc-botosani</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C446" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12190,7 +12200,7 @@
         <v>cfr-cluj</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C447" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12211,7 +12221,7 @@
         <v>corvinul-hunedoara</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="C448" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12232,7 +12242,7 @@
         <v>fk-miercurea-ciuc</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C449" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12253,7 +12263,7 @@
         <v>fc-dinamo-bucuresti</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C450" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12274,7 +12284,7 @@
         <v>fc-farul-constanta</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C451" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12295,7 +12305,7 @@
         <v>fc-arges-pitesti</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="C452" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12316,7 +12326,7 @@
         <v>fc-rapid-bucuresti</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="C453" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12337,7 +12347,7 @@
         <v>fc-voluntari</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="C454" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12358,7 +12368,7 @@
         <v>fcsb</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="C455" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12379,7 +12389,7 @@
         <v>asc-otelul-galati</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="C456" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12400,7 +12410,7 @@
         <v>fc-petrolul-ploiesti</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="C457" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12421,7 +12431,7 @@
         <v>sepsi-osk-sftantu-gheorghe</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="C458" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12442,7 +12452,7 @@
         <v>fc-universitatea-cluj</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C459" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12463,7 +12473,7 @@
         <v>cs-universitatea-craiova</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="C460" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12484,7 +12494,7 @@
         <v>fc-uta-arad</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C461" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12505,7 +12515,7 @@
         <v>abha-club</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="C462" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12526,7 +12536,7 @@
         <v>diriyah-club</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="C463" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12547,7 +12557,7 @@
         <v>al-fateh-sc</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C464" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12568,7 +12578,7 @@
         <v>al-fayha-fc</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C465" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12589,7 +12599,7 @@
         <v>al-hazem-fc</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C466" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12610,7 +12620,7 @@
         <v>khaleej-fc</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C467" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12631,7 +12641,7 @@
         <v>al-kholood-club</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C468" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12652,7 +12662,7 @@
         <v>al-qadsiah-fc</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="C469" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12673,7 +12683,7 @@
         <v>al-riyadh-sc</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="C470" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12694,7 +12704,7 @@
         <v>al-ahli-saudi-fc</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C471" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12715,7 +12725,7 @@
         <v>al-ettifaq-fc</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C472" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12736,7 +12746,7 @@
         <v>al-faisaly-fc</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="C473" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12757,7 +12767,7 @@
         <v>al-hilal-fc</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C474" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12778,7 +12788,7 @@
         <v>al-ittihad-fc</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C475" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12799,7 +12809,7 @@
         <v>al-nassr-fc</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C476" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12820,7 +12830,7 @@
         <v>al-shabab-fc</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C477" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12841,7 +12851,7 @@
         <v>al-taawoun-fc</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C478" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12862,7 +12872,7 @@
         <v>neom-sc</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="C479" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12883,7 +12893,7 @@
         <v>aberdeen-fc</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="C480" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12904,7 +12914,7 @@
         <v>celtic-fc</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C481" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12925,7 +12935,7 @@
         <v>dundee-fc</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="C482" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12946,7 +12956,7 @@
         <v>dundee-united-fc</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C483" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12967,7 +12977,7 @@
         <v>falkirk-fc</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C484" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12988,7 +12998,7 @@
         <v>heart-of-midlothian-fc</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C485" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13009,7 +13019,7 @@
         <v>hibernian-fc</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C486" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13030,7 +13040,7 @@
         <v>kilmarnock-fc</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C487" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13051,7 +13061,7 @@
         <v>motherwell-fc</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C488" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13072,7 +13082,7 @@
         <v>rangers-fc</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C489" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13093,7 +13103,7 @@
         <v>st-johnstone-fc</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="C490" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13114,7 +13124,7 @@
         <v>st-mirren-fc</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C491" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13132,10 +13142,10 @@
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-alaves</v>
+        <v>deportivo-de-a-coruna</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>40</v>
+        <v>621</v>
       </c>
       <c r="C492" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13147,16 +13157,16 @@
       </c>
       <c r="E492" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>athletic-bilbao</v>
+        <v>deportivo-alaves</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C493" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13168,16 +13178,16 @@
       </c>
       <c r="E493" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-madrid</v>
+        <v>athletic-bilbao</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C494" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13189,16 +13199,16 @@
       </c>
       <c r="E494" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-barcelona</v>
+        <v>atletico-madrid</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C495" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13210,16 +13220,16 @@
       </c>
       <c r="E495" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-betis-balompie</v>
+        <v>fc-barcelona</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C496" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13231,16 +13241,16 @@
       </c>
       <c r="E496" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>celta-vigo</v>
+        <v>real-betis-balompie</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C497" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13252,16 +13262,16 @@
       </c>
       <c r="E497" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>elche-cf</v>
+        <v>celta-vigo</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>492</v>
+        <v>45</v>
       </c>
       <c r="C498" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13273,16 +13283,16 @@
       </c>
       <c r="E498" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rcd-espanyol</v>
+        <v>elche-cf</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="C499" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13294,16 +13304,16 @@
       </c>
       <c r="E499" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>getafe-cf</v>
+        <v>rcd-espanyol</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C500" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13315,16 +13325,16 @@
       </c>
       <c r="E500" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>girona-fc</v>
+        <v>getafe-cf</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C501" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13336,7 +13346,7 @@
       </c>
       <c r="E501" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
@@ -13345,7 +13355,7 @@
         <v>levante-ud</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C502" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13357,16 +13367,16 @@
       </c>
       <c r="E502" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rcd-mallorca</v>
+        <v>malaga-cf</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>51</v>
+        <v>409</v>
       </c>
       <c r="C503" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13378,7 +13388,7 @@
       </c>
       <c r="E503" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
@@ -13399,16 +13409,16 @@
       </c>
       <c r="E504" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-oviedo</v>
+        <v>racing-de-santander</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>494</v>
+        <v>410</v>
       </c>
       <c r="C505" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13420,7 +13430,7 @@
       </c>
       <c r="E505" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.3">
@@ -13441,7 +13451,7 @@
       </c>
       <c r="E506" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.3">
@@ -13462,7 +13472,7 @@
       </c>
       <c r="E507" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
@@ -13483,7 +13493,7 @@
       </c>
       <c r="E508" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.3">
@@ -13504,7 +13514,7 @@
       </c>
       <c r="E509" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.3">
@@ -13525,7 +13535,7 @@
       </c>
       <c r="E510" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.3">
@@ -13546,7 +13556,7 @@
       </c>
       <c r="E511" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.3">
@@ -13555,18 +13565,18 @@
         <v>albacete-balompie</v>
       </c>
       <c r="B512" s="5" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="C512" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D512" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E512" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.3">
@@ -13575,18 +13585,18 @@
         <v>ud-almeria</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C513" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D513" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E513" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.3">
@@ -13595,18 +13605,18 @@
         <v>fc-andorra</v>
       </c>
       <c r="B514" s="5" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="C514" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D514" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E514" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.3">
@@ -13615,18 +13625,18 @@
         <v>burgos-cf</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C515" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D515" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E515" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.3">
@@ -13635,18 +13645,18 @@
         <v>cadiz-cf</v>
       </c>
       <c r="B516" s="5" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C516" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D516" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E516" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.3">
@@ -13655,78 +13665,78 @@
         <v>cd-castellon</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C517" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D517" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E517" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ad-ceuta-fc</v>
+        <v>celta-de-vigo-b</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>481</v>
+        <v>622</v>
       </c>
       <c r="C518" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D518" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E518" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cordoba-cf</v>
+        <v>ad-ceuta-fc</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C519" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D519" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E519" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cultural-y-deportiva-leonesa</v>
+        <v>cordoba-cf</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>482</v>
+        <v>405</v>
       </c>
       <c r="C520" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D520" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E520" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.3">
@@ -13735,98 +13745,98 @@
         <v>sd-eibar</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C521" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D521" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E521" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-de-gijon</v>
+        <v>cd-eldense</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>418</v>
+        <v>623</v>
       </c>
       <c r="C522" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D522" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E522" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>granada-cf</v>
+        <v>sporting-de-gijon</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C523" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D523" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E523" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sd-huesca</v>
+        <v>girona-fc</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>420</v>
+        <v>48</v>
       </c>
       <c r="C524" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D524" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E524" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-de-la-coruna</v>
+        <v>granada-cf</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="C525" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D525" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E525" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.3">
@@ -13842,11 +13852,11 @@
         <v>spain</v>
       </c>
       <c r="D526" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E526" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.3">
@@ -13862,131 +13872,131 @@
         <v>spain</v>
       </c>
       <c r="D527" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E527" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>malaga-cf</v>
+        <v>rcd-mallorca</v>
       </c>
       <c r="B528" s="5" t="s">
-        <v>422</v>
+        <v>51</v>
       </c>
       <c r="C528" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D528" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E528" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-mirandes</v>
+        <v>real-oviedo</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="C529" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D529" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E529" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>racing-de-santander</v>
+        <v>real-sociedad-b</v>
       </c>
       <c r="B530" s="5" t="s">
-        <v>424</v>
+        <v>467</v>
       </c>
       <c r="C530" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D530" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E530" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-sociedad-b</v>
+        <v>ce-sabadell-fc</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>483</v>
+        <v>624</v>
       </c>
       <c r="C531" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D531" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E531" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-valladolid</v>
+        <v>cd-tenerife</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>58</v>
+        <v>625</v>
       </c>
       <c r="C532" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D532" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E532" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-zaragoza</v>
+        <v>real-valladolid</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>425</v>
+        <v>58</v>
       </c>
       <c r="C533" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D533" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="E533" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.3">
@@ -13995,7 +14005,7 @@
         <v>aik</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C534" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14016,7 +14026,7 @@
         <v>if-brommapojkarna</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C535" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14037,7 +14047,7 @@
         <v>degerfors-if</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="C536" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14058,7 +14068,7 @@
         <v>djurgardens-if</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C537" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14079,7 +14089,7 @@
         <v>if-elfsborg</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C538" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14100,7 +14110,7 @@
         <v>gais</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C539" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14121,7 +14131,7 @@
         <v>ifk-goteborg</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C540" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14142,7 +14152,7 @@
         <v>bk-hacken</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="C541" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14163,7 +14173,7 @@
         <v>halmstads-bk</v>
       </c>
       <c r="B542" s="5" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C542" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14184,7 +14194,7 @@
         <v>hammarby-if</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C543" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14205,7 +14215,7 @@
         <v>kalmar-ff</v>
       </c>
       <c r="B544" s="5" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="C544" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14226,7 +14236,7 @@
         <v>malmo-ff</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="C545" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14247,7 +14257,7 @@
         <v>mjallby-aif</v>
       </c>
       <c r="B546" s="5" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="C546" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14268,7 +14278,7 @@
         <v>orgryte-is</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="C547" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14289,7 +14299,7 @@
         <v>ik-sirius</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C548" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14310,7 +14320,7 @@
         <v>vasteras-sk</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="C549" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14331,7 +14341,7 @@
         <v>fc-basel</v>
       </c>
       <c r="B550" s="5" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="C550" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14352,7 +14362,7 @@
         <v>grasshopper-club-zurich</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C551" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14373,7 +14383,7 @@
         <v>fc-lausanne-sport</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="C552" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14394,7 +14404,7 @@
         <v>fc-lugano</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="C553" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14415,7 +14425,7 @@
         <v>fc-luzern</v>
       </c>
       <c r="B554" s="5" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C554" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14436,7 +14446,7 @@
         <v>servette-fc</v>
       </c>
       <c r="B555" s="6" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C555" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14457,7 +14467,7 @@
         <v>fc-sion</v>
       </c>
       <c r="B556" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C556" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14478,7 +14488,7 @@
         <v>fc-st-gallen</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="C557" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14499,7 +14509,7 @@
         <v>fc-thun</v>
       </c>
       <c r="B558" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="C558" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14520,7 +14530,7 @@
         <v>fc-vaduz</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="C559" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14541,7 +14551,7 @@
         <v>bsc-young-boys</v>
       </c>
       <c r="B560" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C560" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14562,7 +14572,7 @@
         <v>fc-zurich</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="C561" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14583,7 +14593,7 @@
         <v>atlanta-united-fc</v>
       </c>
       <c r="B562" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C562" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14604,7 +14614,7 @@
         <v>austin-fc</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="C563" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14625,7 +14635,7 @@
         <v>club-de-foot-montreal</v>
       </c>
       <c r="B564" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="C564" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14646,7 +14656,7 @@
         <v>charlotte-fc</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="C565" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14667,7 +14677,7 @@
         <v>chicago-fire-fc</v>
       </c>
       <c r="B566" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="C566" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14688,7 +14698,7 @@
         <v>fc-cincinnati</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C567" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14709,7 +14719,7 @@
         <v>colorado-rapids</v>
       </c>
       <c r="B568" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="C568" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14730,7 +14740,7 @@
         <v>columbus-crew-sc</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="C569" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14751,7 +14761,7 @@
         <v>dc-united</v>
       </c>
       <c r="B570" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="C570" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14772,7 +14782,7 @@
         <v>fc-dallas</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="C571" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14793,7 +14803,7 @@
         <v>houston-dynamo</v>
       </c>
       <c r="B572" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="C572" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14814,7 +14824,7 @@
         <v>inter-miami-cf</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="C573" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14835,7 +14845,7 @@
         <v>los-angeles-fc</v>
       </c>
       <c r="B574" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="C574" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14856,7 +14866,7 @@
         <v>los-angeles-galaxy</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C575" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14877,7 +14887,7 @@
         <v>minnesota-united-fc</v>
       </c>
       <c r="B576" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="C576" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14898,7 +14908,7 @@
         <v>nashville-sc</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="C577" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14919,7 +14929,7 @@
         <v>new-england-revolution</v>
       </c>
       <c r="B578" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="C578" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14940,7 +14950,7 @@
         <v>new-york-city-fc</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C579" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14961,7 +14971,7 @@
         <v>new-york-red-bulls</v>
       </c>
       <c r="B580" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C580" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14982,7 +14992,7 @@
         <v>orlando-city-sc</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="C581" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15003,7 +15013,7 @@
         <v>philadelphia-union</v>
       </c>
       <c r="B582" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="C582" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15024,7 +15034,7 @@
         <v>portland-timbers</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C583" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15045,7 +15055,7 @@
         <v>real-salt-lake</v>
       </c>
       <c r="B584" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="C584" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15066,7 +15076,7 @@
         <v>san-diego-fc</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="C585" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15087,7 +15097,7 @@
         <v>san-jose-earthquakes</v>
       </c>
       <c r="B586" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="C586" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15108,7 +15118,7 @@
         <v>seattle-sounders-fc</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C587" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15129,7 +15139,7 @@
         <v>sporting-kansas-city</v>
       </c>
       <c r="B588" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C588" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15150,7 +15160,7 @@
         <v>st-louis-city-sc</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="C589" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15171,7 +15181,7 @@
         <v>toronto-fc</v>
       </c>
       <c r="B590" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="C590" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15192,7 +15202,7 @@
         <v>vancouver-whitecaps-fc</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C591" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15213,7 +15223,7 @@
         <v>bohemians-fc</v>
       </c>
       <c r="B592" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="C592" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15234,7 +15244,7 @@
         <v>derry-city-fc</v>
       </c>
       <c r="B593" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="C593" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15255,7 +15265,7 @@
         <v>drogheda-united-fc</v>
       </c>
       <c r="B594" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="C594" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15276,7 +15286,7 @@
         <v>dundalk-fc</v>
       </c>
       <c r="B595" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="C595" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15297,7 +15307,7 @@
         <v>galway-united-fc</v>
       </c>
       <c r="B596" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="C596" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15318,7 +15328,7 @@
         <v>shamrock-rovers-fc</v>
       </c>
       <c r="B597" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="C597" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15339,7 +15349,7 @@
         <v>shelbourne-fc</v>
       </c>
       <c r="B598" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="C598" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15360,7 +15370,7 @@
         <v>sligo-rovers-fc</v>
       </c>
       <c r="B599" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="C599" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15381,7 +15391,7 @@
         <v>st-patricks-athletic-fc</v>
       </c>
       <c r="B600" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="C600" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15402,7 +15412,7 @@
         <v>waterford-fc</v>
       </c>
       <c r="B601" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="C601" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15423,7 +15433,7 @@
         <v>al-ahly-sc</v>
       </c>
       <c r="B602" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="C602" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15444,7 +15454,7 @@
         <v>al-ittihad-ac</v>
       </c>
       <c r="B603" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C603" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15465,7 +15475,7 @@
         <v>al-masry-sc</v>
       </c>
       <c r="B604" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="C604" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15486,7 +15496,7 @@
         <v>arab-contractors-sc</v>
       </c>
       <c r="B605" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="C605" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15507,7 +15517,7 @@
         <v>ceramica-cleopatra-fc</v>
       </c>
       <c r="B606" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="C606" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15528,7 +15538,7 @@
         <v>talaea-el-gaish-sc</v>
       </c>
       <c r="B607" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="C607" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15549,7 +15559,7 @@
         <v>el-gouna-fc</v>
       </c>
       <c r="B608" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="C608" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15570,7 +15580,7 @@
         <v>enppi-sc</v>
       </c>
       <c r="B609" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="C609" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15591,7 +15601,7 @@
         <v>ghazi-el-mahalla-sc</v>
       </c>
       <c r="B610" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="C610" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15612,7 +15622,7 @@
         <v>haras-el-hodoud-sc</v>
       </c>
       <c r="B611" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="C611" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15633,7 +15643,7 @@
         <v>ismaily-sc</v>
       </c>
       <c r="B612" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="C612" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15654,7 +15664,7 @@
         <v>kahrabaa-ismailia-sc</v>
       </c>
       <c r="B613" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="C613" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15675,7 +15685,7 @@
         <v>modern-sport-fc</v>
       </c>
       <c r="B614" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="C614" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15696,7 +15706,7 @@
         <v>national-bank-of-egypt-sc</v>
       </c>
       <c r="B615" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="C615" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15717,7 +15727,7 @@
         <v>petrojet-sc</v>
       </c>
       <c r="B616" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="C616" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15738,7 +15748,7 @@
         <v>pharco-fc</v>
       </c>
       <c r="B617" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="C617" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15759,7 +15769,7 @@
         <v>pyramids-fc</v>
       </c>
       <c r="B618" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="C618" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15780,7 +15790,7 @@
         <v>smouha-sc</v>
       </c>
       <c r="B619" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="C619" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15801,7 +15811,7 @@
         <v>wadi-degla-sc</v>
       </c>
       <c r="B620" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="C620" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15822,7 +15832,7 @@
         <v>zamalek-sc</v>
       </c>
       <c r="B621" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="C621" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15843,7 +15853,7 @@
         <v>zed-fc</v>
       </c>
       <c r="B622" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="C622" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
